--- a/design/data-model.xlsx
+++ b/design/data-model.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devankshi/Desktop/projects/enterprise-ecommerce-system/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2C8364-07AC-A847-8731-79514ECF0B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A43879-C496-F24E-AF36-340477F28062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16700" xr2:uid="{B4B0CF1E-33F3-D545-AD19-7398141B1839}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16700" activeTab="1" xr2:uid="{B4B0CF1E-33F3-D545-AD19-7398141B1839}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="concept" sheetId="1" r:id="rId1"/>
+    <sheet name="logic" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,9 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="152">
   <si>
     <t>user</t>
+  </si>
+  <si>
+    <t>vendor</t>
   </si>
   <si>
     <t>product</t>
@@ -196,16 +200,320 @@
   </si>
   <si>
     <t>buyer, vendor, admin</t>
+  </si>
+  <si>
+    <t>attributes</t>
+  </si>
+  <si>
+    <t>vendor_product</t>
+  </si>
+  <si>
+    <t>associative entity between vendor and product</t>
+  </si>
+  <si>
+    <t>price, stock, condition, discount, status</t>
+  </si>
+  <si>
+    <t>order_id</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>vendor_id</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>payment_id</t>
+  </si>
+  <si>
+    <t>shipment_id</t>
+  </si>
+  <si>
+    <t>tracking_number</t>
+  </si>
+  <si>
+    <t>order_item</t>
+  </si>
+  <si>
+    <t>order_item_id</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>category_id</t>
+  </si>
+  <si>
+    <t>category_name</t>
+  </si>
+  <si>
+    <t>product_category</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>1NF</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>price_at_purchase</t>
+  </si>
+  <si>
+    <t>order_id *</t>
+  </si>
+  <si>
+    <t>product_id *</t>
+  </si>
+  <si>
+    <t>user_id *</t>
+  </si>
+  <si>
+    <t>vendor_id *</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>role_id</t>
+  </si>
+  <si>
+    <t>role_id *</t>
+  </si>
+  <si>
+    <t>brand</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>category_id *</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>reference_number</t>
+  </si>
+  <si>
+    <t>shipped_at</t>
+  </si>
+  <si>
+    <t>delivered_at</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>address_id</t>
+  </si>
+  <si>
+    <t>street</t>
+  </si>
+  <si>
+    <t>apartment</t>
+  </si>
+  <si>
+    <t>zip</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>address_id *</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>cart_item</t>
+  </si>
+  <si>
+    <t>cart_id</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>cart_item_id</t>
+  </si>
+  <si>
+    <t>vendor_product_id</t>
+  </si>
+  <si>
+    <t>discount</t>
+  </si>
+  <si>
+    <t>condition</t>
+  </si>
+  <si>
+    <t>review_id</t>
+  </si>
+  <si>
+    <t>rating</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>inventory_id</t>
+  </si>
+  <si>
+    <t>quantity_available</t>
+  </si>
+  <si>
+    <t>last_updated</t>
+  </si>
+  <si>
+    <t>vendor_product_id *</t>
+  </si>
+  <si>
+    <t>cart_id *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  order_id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  order_created_at,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  user_id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  first_name,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  last_name,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  email,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  password,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  role_type,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  street,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  city,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  state,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  zip,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  product_id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  product_name,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  product_description,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  brand,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  category_name,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  vendor_id,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  vendor_name,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  vendor_status,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  quantity,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  price,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  discount,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  payment_method,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  payment_status,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  shipment_status,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  tracking_number</t>
+  </si>
+  <si>
+    <t>2NF</t>
+  </si>
+  <si>
+    <t>3NF</t>
+  </si>
+  <si>
+    <t>role_type</t>
+  </si>
+  <si>
+    <t>category_desc</t>
+  </si>
+  <si>
+    <t>separated product and category</t>
+  </si>
+  <si>
+    <t>role separated from user</t>
+  </si>
+  <si>
+    <t>address separated from user</t>
+  </si>
+  <si>
+    <t>0NF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -217,16 +525,42 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -234,14 +568,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -251,6 +703,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,282 +1066,2822 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717ABC26-EFA5-3F42-AA2D-7F24864C2DB2}">
-  <dimension ref="B2:E41"/>
+  <dimension ref="B2:F41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="60.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.5" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B7" s="5">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="5">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="5">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B11" s="5">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="5">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="5">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="5">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="2:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="B15" s="5">
         <v>12</v>
       </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" s="4">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="6">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="6">
+        <v>14</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="D27" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="4">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="2:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="4">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="4">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B9" s="4">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="4">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="2:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="4">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B12" s="4">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B13" s="4">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B14" s="4">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="2:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="B15" s="4">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B16" s="5">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="E22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="E24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D25" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="E26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.2">
-      <c r="D27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="D29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="D31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D35" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D41" t="s">
-        <v>42</v>
-      </c>
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{308AE71A-012C-DC48-8698-7BEF639FACAA}">
+  <dimension ref="B2:AV81"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="25"/>
+    </row>
+    <row r="5" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B5" s="26"/>
+      <c r="C5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="N5" s="28"/>
+    </row>
+    <row r="6" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B6" s="26"/>
+      <c r="C6" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="N6" s="28"/>
+    </row>
+    <row r="7" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B7" s="26"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N7" s="28"/>
+    </row>
+    <row r="8" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B8" s="26"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N8" s="28"/>
+    </row>
+    <row r="9" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B9" s="26"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="28"/>
+    </row>
+    <row r="10" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B10" s="26"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="28"/>
+    </row>
+    <row r="11" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B11" s="26"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="28"/>
+    </row>
+    <row r="12" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B12" s="26"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="28"/>
+    </row>
+    <row r="13" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B13" s="26"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="28"/>
+    </row>
+    <row r="14" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B14" s="26"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="28"/>
+    </row>
+    <row r="15" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="33"/>
+    </row>
+    <row r="16" spans="2:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+      <c r="AG16"/>
+      <c r="AH16"/>
+    </row>
+    <row r="17" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+    </row>
+    <row r="18" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B18" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B20" s="22"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="24"/>
+      <c r="X20" s="24"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="25"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+      <c r="AP20" s="1"/>
+      <c r="AQ20" s="1"/>
+      <c r="AR20" s="1"/>
+      <c r="AS20" s="1"/>
+      <c r="AT20" s="1"/>
+      <c r="AU20" s="1"/>
+      <c r="AV20" s="1"/>
+    </row>
+    <row r="21" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B21" s="34"/>
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+    </row>
+    <row r="22" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="26"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="28"/>
+    </row>
+    <row r="23" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B23" s="26"/>
+      <c r="C23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="R23" s="2"/>
+      <c r="S23" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="T23" s="2"/>
+      <c r="U23" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="V23" s="2"/>
+      <c r="W23" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z23" s="28"/>
+    </row>
+    <row r="24" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B24" s="26"/>
+      <c r="C24" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="R24" s="2"/>
+      <c r="S24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="T24" s="2"/>
+      <c r="U24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="V24" s="2"/>
+      <c r="W24" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z24" s="28"/>
+    </row>
+    <row r="25" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="26"/>
+      <c r="C25" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="R25" s="2"/>
+      <c r="S25" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="T25" s="2"/>
+      <c r="U25" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="V25" s="2"/>
+      <c r="W25" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z25" s="28"/>
+    </row>
+    <row r="26" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="26"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="R26" s="2"/>
+      <c r="S26" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="T26" s="2"/>
+      <c r="U26" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="V26" s="2"/>
+      <c r="W26" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z26" s="28"/>
+    </row>
+    <row r="27" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="26"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="V27" s="2"/>
+      <c r="W27" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="28"/>
+    </row>
+    <row r="28" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="26"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="V28" s="2"/>
+      <c r="W28" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="28"/>
+    </row>
+    <row r="29" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="26"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="28"/>
+    </row>
+    <row r="30" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="26"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="28"/>
+    </row>
+    <row r="31" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B31" s="26"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="28"/>
+    </row>
+    <row r="32" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B32" s="26"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="28"/>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B33" s="26"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="28"/>
+    </row>
+    <row r="34" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="26"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="28"/>
+    </row>
+    <row r="35" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="30"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+      <c r="Z35" s="33"/>
+    </row>
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B38" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B40" s="22"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="24"/>
+      <c r="T40" s="24"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="24"/>
+      <c r="W40" s="24"/>
+      <c r="X40" s="24"/>
+      <c r="Y40" s="24"/>
+      <c r="Z40" s="24"/>
+      <c r="AA40" s="24"/>
+      <c r="AB40" s="24"/>
+      <c r="AC40" s="24"/>
+      <c r="AD40" s="25"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B41" s="26"/>
+      <c r="C41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB41" s="2"/>
+      <c r="AC41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD41" s="28"/>
+    </row>
+    <row r="42" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="26"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="28"/>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="B43" s="26"/>
+      <c r="C43" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="R43" s="2"/>
+      <c r="S43" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="T43" s="2"/>
+      <c r="U43" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="V43" s="2"/>
+      <c r="W43" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB43" s="2"/>
+      <c r="AC43" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD43" s="28"/>
+    </row>
+    <row r="44" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="26"/>
+      <c r="C44" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="2"/>
+      <c r="E44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="R44" s="2"/>
+      <c r="S44" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="T44" s="2"/>
+      <c r="U44" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="V44" s="2"/>
+      <c r="W44" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z44" s="2"/>
+      <c r="AA44" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB44" s="2"/>
+      <c r="AC44" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD44" s="28"/>
+    </row>
+    <row r="45" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="26"/>
+      <c r="C45" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="R45" s="2"/>
+      <c r="S45" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="T45" s="2"/>
+      <c r="U45" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="V45" s="2"/>
+      <c r="W45" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="X45" s="2"/>
+      <c r="Y45" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z45" s="2"/>
+      <c r="AA45" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB45" s="2"/>
+      <c r="AC45" s="2"/>
+      <c r="AD45" s="28"/>
+    </row>
+    <row r="46" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="26"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L46" s="2"/>
+      <c r="M46" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="R46" s="2"/>
+      <c r="S46" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="T46" s="2"/>
+      <c r="U46" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="V46" s="2"/>
+      <c r="W46" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="2"/>
+      <c r="AC46" s="2"/>
+      <c r="AD46" s="28"/>
+    </row>
+    <row r="47" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="26"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L47" s="2"/>
+      <c r="M47" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="V47" s="2"/>
+      <c r="W47" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="28"/>
+    </row>
+    <row r="48" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="26"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="2"/>
+      <c r="U48" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="V48" s="2"/>
+      <c r="W48" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2"/>
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="28"/>
+    </row>
+    <row r="49" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="26"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+      <c r="T49" s="2"/>
+      <c r="U49" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="V49" s="2"/>
+      <c r="W49" s="2"/>
+      <c r="X49" s="2"/>
+      <c r="Y49" s="2"/>
+      <c r="Z49" s="2"/>
+      <c r="AA49" s="2"/>
+      <c r="AB49" s="2"/>
+      <c r="AC49" s="2"/>
+      <c r="AD49" s="28"/>
+    </row>
+    <row r="50" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="26"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
+      <c r="U50" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="V50" s="2"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="28"/>
+    </row>
+    <row r="51" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B51" s="26"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="2"/>
+      <c r="X51" s="2"/>
+      <c r="Y51" s="2"/>
+      <c r="Z51" s="2"/>
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="2"/>
+      <c r="AC51" s="2"/>
+      <c r="AD51" s="28"/>
+    </row>
+    <row r="52" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B52" s="26"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="2"/>
+      <c r="AC52" s="2"/>
+      <c r="AD52" s="28"/>
+    </row>
+    <row r="53" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B53" s="26"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="2"/>
+      <c r="Z53" s="2"/>
+      <c r="AA53" s="2"/>
+      <c r="AB53" s="2"/>
+      <c r="AC53" s="2"/>
+      <c r="AD53" s="28"/>
+    </row>
+    <row r="54" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="26"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="2"/>
+      <c r="Z54" s="2"/>
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="2"/>
+      <c r="AC54" s="2"/>
+      <c r="AD54" s="28"/>
+    </row>
+    <row r="55" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="30"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="32"/>
+      <c r="Y55" s="32"/>
+      <c r="Z55" s="32"/>
+      <c r="AA55" s="32"/>
+      <c r="AB55" s="32"/>
+      <c r="AC55" s="32"/>
+      <c r="AD55" s="33"/>
+    </row>
+    <row r="58" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B58" s="15" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+      <c r="N59" s="16"/>
+      <c r="O59" s="16"/>
+      <c r="P59" s="16"/>
+      <c r="Q59" s="16"/>
+      <c r="R59" s="16"/>
+      <c r="S59" s="16"/>
+      <c r="T59" s="16"/>
+      <c r="U59" s="16"/>
+      <c r="V59" s="16"/>
+      <c r="W59" s="16"/>
+      <c r="X59" s="16"/>
+      <c r="Y59" s="16"/>
+      <c r="Z59" s="16"/>
+      <c r="AA59" s="16"/>
+      <c r="AB59" s="16"/>
+      <c r="AC59" s="16"/>
+    </row>
+    <row r="60" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B60" s="22"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+      <c r="H60" s="23"/>
+      <c r="I60" s="23"/>
+      <c r="J60" s="23"/>
+      <c r="K60" s="23"/>
+      <c r="L60" s="23"/>
+      <c r="M60" s="23"/>
+      <c r="N60" s="23"/>
+      <c r="O60" s="23"/>
+      <c r="P60" s="23"/>
+      <c r="Q60" s="23"/>
+      <c r="R60" s="23"/>
+      <c r="S60" s="23"/>
+      <c r="T60" s="23"/>
+      <c r="U60" s="23"/>
+      <c r="V60" s="23"/>
+      <c r="W60" s="23"/>
+      <c r="X60" s="23"/>
+      <c r="Y60" s="23"/>
+      <c r="Z60" s="23"/>
+      <c r="AA60" s="23"/>
+      <c r="AB60" s="23"/>
+      <c r="AC60" s="23"/>
+      <c r="AD60" s="24"/>
+      <c r="AE60" s="24"/>
+      <c r="AF60" s="24"/>
+      <c r="AG60" s="24"/>
+      <c r="AH60" s="25"/>
+    </row>
+    <row r="61" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B61" s="26"/>
+      <c r="C61" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="J61" s="27"/>
+      <c r="K61" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="R61" s="27"/>
+      <c r="S61" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="T61" s="27"/>
+      <c r="U61" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="V61" s="27"/>
+      <c r="W61" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="X61" s="27"/>
+      <c r="Y61" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z61" s="27"/>
+      <c r="AA61" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB61" s="21"/>
+      <c r="AC61" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD61" s="2"/>
+      <c r="AE61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF61" s="2"/>
+      <c r="AG61" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH61" s="28"/>
+    </row>
+    <row r="62" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="26"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="21"/>
+      <c r="M62" s="21"/>
+      <c r="N62" s="21"/>
+      <c r="O62" s="21"/>
+      <c r="P62" s="21"/>
+      <c r="Q62" s="21"/>
+      <c r="R62" s="21"/>
+      <c r="S62" s="21"/>
+      <c r="T62" s="21"/>
+      <c r="U62" s="21"/>
+      <c r="V62" s="21"/>
+      <c r="W62" s="21"/>
+      <c r="X62" s="21"/>
+      <c r="Y62" s="21"/>
+      <c r="Z62" s="21"/>
+      <c r="AA62" s="21"/>
+      <c r="AB62" s="21"/>
+      <c r="AC62" s="21"/>
+      <c r="AD62" s="2"/>
+      <c r="AE62" s="2"/>
+      <c r="AF62" s="2"/>
+      <c r="AG62" s="2"/>
+      <c r="AH62" s="28"/>
+    </row>
+    <row r="63" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B63" s="26"/>
+      <c r="C63" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="21"/>
+      <c r="E63" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F63" s="21"/>
+      <c r="G63" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H63" s="21"/>
+      <c r="I63" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="J63" s="21"/>
+      <c r="K63" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="L63" s="21"/>
+      <c r="M63" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="N63" s="21"/>
+      <c r="O63" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="P63" s="21"/>
+      <c r="Q63" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="R63" s="21"/>
+      <c r="S63" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="T63" s="21"/>
+      <c r="U63" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="V63" s="21"/>
+      <c r="W63" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="X63" s="21"/>
+      <c r="Y63" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z63" s="21"/>
+      <c r="AA63" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB63" s="21"/>
+      <c r="AC63" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD63" s="2"/>
+      <c r="AE63" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF63" s="2"/>
+      <c r="AG63" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH63" s="28"/>
+    </row>
+    <row r="64" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="26"/>
+      <c r="C64" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" s="21"/>
+      <c r="E64" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="F64" s="21"/>
+      <c r="G64" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="H64" s="21"/>
+      <c r="I64" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="J64" s="21"/>
+      <c r="K64" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="L64" s="21"/>
+      <c r="M64" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="N64" s="21"/>
+      <c r="O64" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="R64" s="21"/>
+      <c r="S64" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="T64" s="21"/>
+      <c r="U64" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="V64" s="21"/>
+      <c r="W64" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="X64" s="21"/>
+      <c r="Y64" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z64" s="21"/>
+      <c r="AA64" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB64" s="21"/>
+      <c r="AC64" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD64" s="2"/>
+      <c r="AE64" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF64" s="2"/>
+      <c r="AG64" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH64" s="28"/>
+    </row>
+    <row r="65" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="26"/>
+      <c r="C65" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D65" s="21"/>
+      <c r="E65" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F65" s="21"/>
+      <c r="G65" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H65" s="21"/>
+      <c r="I65" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="J65" s="21"/>
+      <c r="K65" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" s="21"/>
+      <c r="M65" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N65" s="21"/>
+      <c r="O65" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="P65" s="21"/>
+      <c r="Q65" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="R65" s="21"/>
+      <c r="S65" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="T65" s="21"/>
+      <c r="U65" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="V65" s="21"/>
+      <c r="W65" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="X65" s="21"/>
+      <c r="Y65" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z65" s="21"/>
+      <c r="AA65" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB65" s="21"/>
+      <c r="AC65" s="21"/>
+      <c r="AD65" s="2"/>
+      <c r="AE65" s="2"/>
+      <c r="AF65" s="2"/>
+      <c r="AG65" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH65" s="28"/>
+    </row>
+    <row r="66" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="26"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F66" s="21"/>
+      <c r="G66" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="H66" s="21"/>
+      <c r="I66" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="J66" s="21"/>
+      <c r="K66" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="L66" s="21"/>
+      <c r="M66" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="N66" s="21"/>
+      <c r="O66" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="P66" s="21"/>
+      <c r="Q66" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="R66" s="21"/>
+      <c r="S66" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="T66" s="21"/>
+      <c r="U66" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="V66" s="21"/>
+      <c r="W66" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="X66" s="21"/>
+      <c r="Y66" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z66" s="21"/>
+      <c r="AA66" s="21"/>
+      <c r="AB66" s="21"/>
+      <c r="AC66" s="21"/>
+      <c r="AD66" s="2"/>
+      <c r="AE66" s="2"/>
+      <c r="AF66" s="2"/>
+      <c r="AG66" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH66" s="28"/>
+    </row>
+    <row r="67" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="26"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F67" s="21"/>
+      <c r="G67" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H67" s="21"/>
+      <c r="I67" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="J67" s="21"/>
+      <c r="K67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="L67" s="21"/>
+      <c r="M67" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="N67" s="21"/>
+      <c r="O67" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="P67" s="21"/>
+      <c r="Q67" s="21"/>
+      <c r="R67" s="21"/>
+      <c r="S67" s="21"/>
+      <c r="T67" s="21"/>
+      <c r="U67" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="V67" s="21"/>
+      <c r="W67" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="X67" s="21"/>
+      <c r="Y67" s="21"/>
+      <c r="Z67" s="21"/>
+      <c r="AA67" s="21"/>
+      <c r="AB67" s="21"/>
+      <c r="AC67" s="21"/>
+      <c r="AD67" s="2"/>
+      <c r="AE67" s="2"/>
+      <c r="AF67" s="2"/>
+      <c r="AG67" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH67" s="28"/>
+    </row>
+    <row r="68" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="26"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="L68" s="21"/>
+      <c r="M68" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="N68" s="21"/>
+      <c r="O68" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="V68" s="21"/>
+      <c r="W68" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="X68" s="21"/>
+      <c r="Y68" s="21"/>
+      <c r="Z68" s="21"/>
+      <c r="AA68" s="21"/>
+      <c r="AB68" s="21"/>
+      <c r="AC68" s="21"/>
+      <c r="AD68" s="2"/>
+      <c r="AE68" s="2"/>
+      <c r="AF68" s="2"/>
+      <c r="AG68" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH68" s="28"/>
+    </row>
+    <row r="69" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="26"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="N69" s="21"/>
+      <c r="O69" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P69" s="21"/>
+      <c r="Q69" s="21"/>
+      <c r="R69" s="21"/>
+      <c r="S69" s="21"/>
+      <c r="T69" s="21"/>
+      <c r="U69" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="V69" s="21"/>
+      <c r="W69" s="21"/>
+      <c r="X69" s="21"/>
+      <c r="Y69" s="21"/>
+      <c r="Z69" s="21"/>
+      <c r="AA69" s="21"/>
+      <c r="AB69" s="21"/>
+      <c r="AC69" s="21"/>
+      <c r="AD69" s="2"/>
+      <c r="AE69" s="2"/>
+      <c r="AF69" s="2"/>
+      <c r="AG69" s="2"/>
+      <c r="AH69" s="28"/>
+    </row>
+    <row r="70" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="26"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="21"/>
+      <c r="N70" s="21"/>
+      <c r="O70" s="21"/>
+      <c r="P70" s="21"/>
+      <c r="Q70" s="21"/>
+      <c r="R70" s="21"/>
+      <c r="S70" s="21"/>
+      <c r="T70" s="21"/>
+      <c r="U70" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="V70" s="21"/>
+      <c r="W70" s="21"/>
+      <c r="X70" s="21"/>
+      <c r="Y70" s="21"/>
+      <c r="Z70" s="21"/>
+      <c r="AA70" s="21"/>
+      <c r="AB70" s="21"/>
+      <c r="AC70" s="21"/>
+      <c r="AD70" s="2"/>
+      <c r="AE70" s="2"/>
+      <c r="AF70" s="2"/>
+      <c r="AG70" s="2"/>
+      <c r="AH70" s="28"/>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B71" s="26"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
+      <c r="K71" s="21"/>
+      <c r="L71" s="21"/>
+      <c r="M71" s="21"/>
+      <c r="N71" s="21"/>
+      <c r="O71" s="21"/>
+      <c r="P71" s="21"/>
+      <c r="Q71" s="21"/>
+      <c r="R71" s="21"/>
+      <c r="S71" s="21"/>
+      <c r="T71" s="21"/>
+      <c r="U71" s="21"/>
+      <c r="V71" s="21"/>
+      <c r="W71" s="21"/>
+      <c r="X71" s="21"/>
+      <c r="Y71" s="21"/>
+      <c r="Z71" s="21"/>
+      <c r="AA71" s="21"/>
+      <c r="AB71" s="21"/>
+      <c r="AC71" s="21"/>
+      <c r="AD71" s="2"/>
+      <c r="AE71" s="2"/>
+      <c r="AF71" s="2"/>
+      <c r="AG71" s="2"/>
+      <c r="AH71" s="28"/>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B72" s="26"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+      <c r="O72" s="21"/>
+      <c r="P72" s="21"/>
+      <c r="Q72" s="21"/>
+      <c r="R72" s="21"/>
+      <c r="S72" s="21"/>
+      <c r="T72" s="21"/>
+      <c r="U72" s="21"/>
+      <c r="V72" s="21"/>
+      <c r="W72" s="21"/>
+      <c r="X72" s="21"/>
+      <c r="Y72" s="21"/>
+      <c r="Z72" s="21"/>
+      <c r="AA72" s="21"/>
+      <c r="AB72" s="21"/>
+      <c r="AC72" s="21"/>
+      <c r="AD72" s="2"/>
+      <c r="AE72" s="2"/>
+      <c r="AF72" s="2"/>
+      <c r="AG72" s="2"/>
+      <c r="AH72" s="28"/>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B73" s="26"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
+      <c r="K73" s="21"/>
+      <c r="L73" s="21"/>
+      <c r="M73" s="21"/>
+      <c r="N73" s="21"/>
+      <c r="O73" s="21"/>
+      <c r="P73" s="21"/>
+      <c r="Q73" s="21"/>
+      <c r="R73" s="21"/>
+      <c r="S73" s="21"/>
+      <c r="T73" s="21"/>
+      <c r="U73" s="21"/>
+      <c r="V73" s="21"/>
+      <c r="W73" s="21"/>
+      <c r="X73" s="21"/>
+      <c r="Y73" s="21"/>
+      <c r="Z73" s="21"/>
+      <c r="AA73" s="21"/>
+      <c r="AB73" s="21"/>
+      <c r="AC73" s="21"/>
+      <c r="AD73" s="2"/>
+      <c r="AE73" s="2"/>
+      <c r="AF73" s="2"/>
+      <c r="AG73" s="2"/>
+      <c r="AH73" s="28"/>
+    </row>
+    <row r="74" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="30"/>
+      <c r="C74" s="31"/>
+      <c r="D74" s="31"/>
+      <c r="E74" s="31"/>
+      <c r="F74" s="31"/>
+      <c r="G74" s="31"/>
+      <c r="H74" s="31"/>
+      <c r="I74" s="31"/>
+      <c r="J74" s="31"/>
+      <c r="K74" s="31"/>
+      <c r="L74" s="31"/>
+      <c r="M74" s="31"/>
+      <c r="N74" s="31"/>
+      <c r="O74" s="31"/>
+      <c r="P74" s="31"/>
+      <c r="Q74" s="31"/>
+      <c r="R74" s="31"/>
+      <c r="S74" s="31"/>
+      <c r="T74" s="31"/>
+      <c r="U74" s="31"/>
+      <c r="V74" s="31"/>
+      <c r="W74" s="31"/>
+      <c r="X74" s="31"/>
+      <c r="Y74" s="31"/>
+      <c r="Z74" s="31"/>
+      <c r="AA74" s="31"/>
+      <c r="AB74" s="31"/>
+      <c r="AC74" s="31"/>
+      <c r="AD74" s="32"/>
+      <c r="AE74" s="32"/>
+      <c r="AF74" s="32"/>
+      <c r="AG74" s="32"/>
+      <c r="AH74" s="33"/>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="16"/>
+      <c r="M75" s="16"/>
+      <c r="N75" s="16"/>
+      <c r="O75" s="16"/>
+      <c r="P75" s="16"/>
+      <c r="Q75" s="16"/>
+      <c r="R75" s="16"/>
+      <c r="S75" s="16"/>
+      <c r="T75" s="16"/>
+      <c r="U75" s="16"/>
+      <c r="V75" s="16"/>
+      <c r="W75" s="16"/>
+      <c r="X75" s="16"/>
+      <c r="Y75" s="16"/>
+      <c r="Z75" s="16"/>
+      <c r="AA75" s="16"/>
+      <c r="AB75" s="16"/>
+      <c r="AC75" s="16"/>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="16"/>
+      <c r="N76" s="16"/>
+      <c r="O76" s="16"/>
+      <c r="P76" s="16"/>
+      <c r="Q76" s="16"/>
+      <c r="R76" s="16"/>
+      <c r="S76" s="16"/>
+      <c r="T76" s="16"/>
+      <c r="U76" s="16"/>
+      <c r="V76" s="16"/>
+      <c r="W76" s="16"/>
+      <c r="X76" s="16"/>
+      <c r="Y76" s="16"/>
+      <c r="Z76" s="16"/>
+      <c r="AA76" s="16"/>
+      <c r="AB76" s="16"/>
+      <c r="AC76" s="16"/>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
+      <c r="M77" s="16"/>
+      <c r="N77" s="16"/>
+      <c r="O77" s="16"/>
+      <c r="P77" s="16"/>
+      <c r="Q77" s="16"/>
+      <c r="R77" s="16"/>
+      <c r="S77" s="16"/>
+      <c r="T77" s="16"/>
+      <c r="U77" s="16"/>
+      <c r="V77" s="16"/>
+      <c r="W77" s="16"/>
+      <c r="X77" s="16"/>
+      <c r="Y77" s="16"/>
+      <c r="Z77" s="16"/>
+      <c r="AA77" s="16"/>
+      <c r="AB77" s="16"/>
+      <c r="AC77" s="16"/>
+    </row>
+    <row r="78" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="P78" s="16"/>
+      <c r="Q78" s="16"/>
+      <c r="R78" s="16"/>
+      <c r="S78" s="16"/>
+      <c r="T78" s="16"/>
+      <c r="U78" s="16"/>
+      <c r="V78" s="16"/>
+      <c r="W78" s="16"/>
+      <c r="X78" s="16"/>
+      <c r="Y78" s="16"/>
+      <c r="Z78" s="16"/>
+      <c r="AA78" s="16"/>
+      <c r="AB78" s="16"/>
+      <c r="AC78" s="16"/>
+    </row>
+    <row r="81" spans="16:23" x14ac:dyDescent="0.2">
+      <c r="P81" s="1"/>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/data-model.xlsx
+++ b/design/data-model.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devankshi/Desktop/projects/enterprise-ecommerce-system/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A43879-C496-F24E-AF36-340477F28062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0360D49D-04D1-6A45-96E6-86A02FCA590D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16700" activeTab="1" xr2:uid="{B4B0CF1E-33F3-D545-AD19-7398141B1839}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16700" activeTab="3" xr2:uid="{B4B0CF1E-33F3-D545-AD19-7398141B1839}"/>
   </bookViews>
   <sheets>
     <sheet name="concept" sheetId="1" r:id="rId1"/>
-    <sheet name="logic" sheetId="3" r:id="rId2"/>
+    <sheet name="normalization" sheetId="3" r:id="rId2"/>
+    <sheet name="schema" sheetId="4" r:id="rId3"/>
+    <sheet name="DW" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="195">
   <si>
     <t>user</t>
   </si>
@@ -497,13 +499,142 @@
   </si>
   <si>
     <t>0NF</t>
+  </si>
+  <si>
+    <t>orders</t>
+  </si>
+  <si>
+    <t>users</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>product_name</t>
+  </si>
+  <si>
+    <t>product_brand</t>
+  </si>
+  <si>
+    <t>product_description</t>
+  </si>
+  <si>
+    <t>dim_user</t>
+  </si>
+  <si>
+    <t>dim_product</t>
+  </si>
+  <si>
+    <t>dim_vendor</t>
+  </si>
+  <si>
+    <t>vendor_name</t>
+  </si>
+  <si>
+    <t>approval_status</t>
+  </si>
+  <si>
+    <t>dim_date</t>
+  </si>
+  <si>
+    <t>full_date</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>quarter</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>date_id</t>
+  </si>
+  <si>
+    <t>holiday_flag</t>
+  </si>
+  <si>
+    <t>dim_category</t>
+  </si>
+  <si>
+    <t>shipment_status</t>
+  </si>
+  <si>
+    <t>payment_method</t>
+  </si>
+  <si>
+    <t>fact_order</t>
+  </si>
+  <si>
+    <t>total_amount</t>
+  </si>
+  <si>
+    <t>fact_order_item</t>
+  </si>
+  <si>
+    <t>line_total</t>
+  </si>
+  <si>
+    <t>fact_payment</t>
+  </si>
+  <si>
+    <t>payment_method_id</t>
+  </si>
+  <si>
+    <t>dim_payment_method</t>
+  </si>
+  <si>
+    <t>fact_inventory</t>
+  </si>
+  <si>
+    <t>fact_review</t>
+  </si>
+  <si>
+    <t>given_rating</t>
+  </si>
+  <si>
+    <t>fact_shipment</t>
+  </si>
+  <si>
+    <t>delivery_days</t>
+  </si>
+  <si>
+    <t>shipment_status_id</t>
+  </si>
+  <si>
+    <t>dim_shipment_status</t>
+  </si>
+  <si>
+    <t>fact_cart</t>
+  </si>
+  <si>
+    <t>order_date</t>
+  </si>
+  <si>
+    <t>shipment_date</t>
+  </si>
+  <si>
+    <t>payment_date</t>
+  </si>
+  <si>
+    <t>delivery_date</t>
+  </si>
+  <si>
+    <t>ship_date</t>
+  </si>
+  <si>
+    <t>review_date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -539,8 +670,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -557,6 +720,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -689,49 +858,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1076,199 +1257,185 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D5" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B10" s="5">
+      <c r="B10" s="3">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B11" s="5">
+      <c r="B11" s="3">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B12" s="5">
+      <c r="B12" s="3">
         <v>9</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B13" s="5">
+      <c r="B13" s="3">
         <v>10</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="2"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B14" s="5">
+      <c r="B14" s="3">
         <v>11</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="2:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="B15" s="5">
+      <c r="B15" s="3">
         <v>12</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="6">
+      <c r="B16" s="3">
         <v>13</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="2"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B18" s="6">
+      <c r="B18" s="3">
         <v>14</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D18" t="s">
@@ -1279,7 +1446,7 @@
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B19" s="6">
+      <c r="B19" s="3">
         <v>15</v>
       </c>
     </row>
@@ -1401,238 +1568,155 @@
     </row>
     <row r="3" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B4" s="22"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="25"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B5" s="26"/>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>129</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
+      <c r="I5" t="s">
         <v>134</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
+      <c r="K5" t="s">
         <v>137</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
+      <c r="M5" t="s">
         <v>140</v>
       </c>
-      <c r="N5" s="28"/>
+      <c r="N5" s="20"/>
     </row>
     <row r="6" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B6" s="26"/>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>130</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
+      <c r="I6" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
+      <c r="K6" t="s">
         <v>138</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2" t="s">
+      <c r="M6" t="s">
         <v>141</v>
       </c>
-      <c r="N6" s="28"/>
+      <c r="N6" s="20"/>
     </row>
     <row r="7" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B7" s="26"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
+      <c r="B7" s="19"/>
+      <c r="E7" t="s">
         <v>121</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>131</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
+      <c r="I7" t="s">
         <v>136</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
+      <c r="K7" t="s">
         <v>139</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2" t="s">
+      <c r="M7" t="s">
         <v>142</v>
       </c>
-      <c r="N7" s="28"/>
+      <c r="N7" s="20"/>
     </row>
     <row r="8" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B8" s="26"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
+      <c r="B8" s="19"/>
+      <c r="E8" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
+      <c r="G8" t="s">
         <v>132</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2" t="s">
+      <c r="M8" t="s">
         <v>143</v>
       </c>
-      <c r="N8" s="28"/>
+      <c r="N8" s="20"/>
     </row>
     <row r="9" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B9" s="26"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
+      <c r="B9" s="19"/>
+      <c r="E9" t="s">
         <v>123</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
+      <c r="G9" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="28"/>
+      <c r="N9" s="20"/>
     </row>
     <row r="10" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B10" s="26"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
+      <c r="B10" s="19"/>
+      <c r="E10" t="s">
         <v>124</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="28"/>
+      <c r="N10" s="20"/>
     </row>
     <row r="11" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B11" s="26"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
+      <c r="B11" s="19"/>
+      <c r="E11" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="28"/>
+      <c r="N11" s="20"/>
     </row>
     <row r="12" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B12" s="26"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
+      <c r="B12" s="19"/>
+      <c r="E12" t="s">
         <v>126</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="28"/>
+      <c r="N12" s="20"/>
     </row>
     <row r="13" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B13" s="26"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2" t="s">
+      <c r="B13" s="19"/>
+      <c r="E13" t="s">
         <v>127</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="28"/>
+      <c r="N13" s="20"/>
     </row>
     <row r="14" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B14" s="26"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2" t="s">
+      <c r="B14" s="19"/>
+      <c r="E14" t="s">
         <v>128</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="28"/>
+      <c r="N14" s="20"/>
     </row>
     <row r="15" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="30"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="33"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="24"/>
     </row>
     <row r="16" spans="2:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16"/>
@@ -1711,31 +1795,31 @@
     </row>
     <row r="19" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B20" s="22"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="25"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="18"/>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
@@ -1752,55 +1836,55 @@
       <c r="AV20" s="1"/>
     </row>
     <row r="21" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B21" s="34"/>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="s">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3" t="s">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3" t="s">
+      <c r="H21" s="1"/>
+      <c r="I21" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3" t="s">
+      <c r="J21" s="1"/>
+      <c r="K21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3" t="s">
+      <c r="L21" s="1"/>
+      <c r="M21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3" t="s">
+      <c r="N21" s="1"/>
+      <c r="O21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3" t="s">
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3" t="s">
+      <c r="R21" s="1"/>
+      <c r="S21" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3" t="s">
+      <c r="T21" s="1"/>
+      <c r="U21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3" t="s">
+      <c r="V21" s="1"/>
+      <c r="W21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3" t="s">
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Z21" s="35"/>
+      <c r="Z21" s="26"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
@@ -1811,528 +1895,302 @@
       <c r="AH21" s="1"/>
     </row>
     <row r="22" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="26"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="28"/>
+      <c r="B22" s="19"/>
+      <c r="Z22" s="20"/>
     </row>
     <row r="23" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B23" s="26"/>
-      <c r="C23" s="11" t="s">
+      <c r="B23" s="19"/>
+      <c r="C23" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="11" t="s">
+      <c r="M23" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="11" t="s">
+      <c r="O23" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="11" t="s">
+      <c r="Q23" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="R23" s="2"/>
-      <c r="S23" s="11" t="s">
+      <c r="S23" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="T23" s="2"/>
-      <c r="U23" s="11" t="s">
+      <c r="U23" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="V23" s="2"/>
-      <c r="W23" s="11" t="s">
+      <c r="W23" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="11" t="s">
+      <c r="Y23" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="Z23" s="28"/>
+      <c r="Z23" s="20"/>
     </row>
     <row r="24" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B24" s="26"/>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="19"/>
+      <c r="C24" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="9" t="s">
+      <c r="M24" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="9" t="s">
+      <c r="O24" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="9" t="s">
+      <c r="Q24" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="R24" s="2"/>
-      <c r="S24" s="9" t="s">
+      <c r="S24" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="T24" s="2"/>
-      <c r="U24" s="9" t="s">
+      <c r="U24" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="V24" s="2"/>
-      <c r="W24" s="9" t="s">
+      <c r="W24" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="9" t="s">
+      <c r="Y24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="Z24" s="28"/>
+      <c r="Z24" s="20"/>
     </row>
     <row r="25" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="26"/>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="19"/>
+      <c r="C25" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="9" t="s">
+      <c r="K25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L25" s="2"/>
-      <c r="M25" s="9" t="s">
+      <c r="M25" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="9" t="s">
+      <c r="O25" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="9" t="s">
+      <c r="Q25" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="R25" s="2"/>
-      <c r="S25" s="12" t="s">
+      <c r="S25" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="T25" s="2"/>
-      <c r="U25" s="9" t="s">
+      <c r="U25" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="V25" s="2"/>
-      <c r="W25" s="9" t="s">
+      <c r="W25" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="9" t="s">
+      <c r="Y25" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z25" s="28"/>
+      <c r="Z25" s="20"/>
     </row>
     <row r="26" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="9" t="s">
+      <c r="B26" s="19"/>
+      <c r="E26" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J26" s="2"/>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L26" s="2"/>
-      <c r="M26" s="9" t="s">
+      <c r="M26" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="9" t="s">
+      <c r="O26" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="13" t="s">
+      <c r="Q26" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="R26" s="2"/>
-      <c r="S26" s="13" t="s">
+      <c r="S26" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="T26" s="2"/>
-      <c r="U26" s="9" t="s">
+      <c r="U26" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="V26" s="2"/>
-      <c r="W26" s="9" t="s">
+      <c r="W26" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="13" t="s">
+      <c r="Y26" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Z26" s="28"/>
+      <c r="Z26" s="20"/>
     </row>
     <row r="27" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="10" t="s">
+      <c r="B27" s="19"/>
+      <c r="E27" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="J27" s="2"/>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="9" t="s">
+      <c r="M27" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="9" t="s">
+      <c r="O27" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="9" t="s">
+      <c r="U27" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="V27" s="2"/>
-      <c r="W27" s="12" t="s">
+      <c r="W27" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-      <c r="Z27" s="28"/>
+      <c r="Z27" s="20"/>
     </row>
     <row r="28" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="26"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="9" t="s">
+      <c r="B28" s="19"/>
+      <c r="G28" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="L28" s="2"/>
-      <c r="M28" s="9" t="s">
+      <c r="M28" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="9" t="s">
+      <c r="O28" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="2"/>
-      <c r="T28" s="2"/>
-      <c r="U28" s="9" t="s">
+      <c r="U28" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="V28" s="2"/>
-      <c r="W28" s="13" t="s">
+      <c r="W28" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="28"/>
+      <c r="Z28" s="20"/>
     </row>
     <row r="29" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="26"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="9" t="s">
+      <c r="B29" s="19"/>
+      <c r="G29" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="L29" s="2"/>
-      <c r="M29" s="10" t="s">
+      <c r="M29" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="10" t="s">
+      <c r="O29" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="12" t="s">
+      <c r="U29" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="28"/>
+      <c r="Z29" s="20"/>
     </row>
     <row r="30" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="26"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="9" t="s">
+      <c r="B30" s="19"/>
+      <c r="G30" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="10" t="s">
+      <c r="K30" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="2"/>
-      <c r="T30" s="2"/>
-      <c r="U30" s="13" t="s">
+      <c r="U30" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="V30" s="2"/>
-      <c r="W30" s="2"/>
-      <c r="X30" s="2"/>
-      <c r="Y30" s="2"/>
-      <c r="Z30" s="28"/>
+      <c r="Z30" s="20"/>
     </row>
     <row r="31" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B31" s="26"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="9" t="s">
+      <c r="B31" s="19"/>
+      <c r="G31" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="2"/>
-      <c r="T31" s="2"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
-      <c r="X31" s="2"/>
-      <c r="Y31" s="2"/>
-      <c r="Z31" s="28"/>
+      <c r="Z31" s="20"/>
     </row>
     <row r="32" spans="2:48" x14ac:dyDescent="0.2">
-      <c r="B32" s="26"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="9" t="s">
+      <c r="B32" s="19"/>
+      <c r="G32" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="28"/>
+      <c r="Z32" s="20"/>
     </row>
     <row r="33" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B33" s="26"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="9" t="s">
+      <c r="B33" s="19"/>
+      <c r="G33" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="28"/>
+      <c r="Z33" s="20"/>
     </row>
     <row r="34" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="26"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="10" t="s">
+      <c r="B34" s="19"/>
+      <c r="G34" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="2"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="2"/>
-      <c r="W34" s="2"/>
-      <c r="X34" s="2"/>
-      <c r="Y34" s="2"/>
-      <c r="Z34" s="28"/>
+      <c r="Z34" s="20"/>
     </row>
     <row r="35" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="30"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="32"/>
-      <c r="R35" s="32"/>
-      <c r="S35" s="32"/>
-      <c r="T35" s="32"/>
-      <c r="U35" s="32"/>
-      <c r="V35" s="32"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="32"/>
-      <c r="Y35" s="32"/>
-      <c r="Z35" s="33"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="23"/>
+      <c r="U35" s="23"/>
+      <c r="V35" s="23"/>
+      <c r="W35" s="23"/>
+      <c r="X35" s="23"/>
+      <c r="Y35" s="23"/>
+      <c r="Z35" s="24"/>
     </row>
     <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B38" s="1" t="s">
@@ -2341,1537 +2199,1220 @@
     </row>
     <row r="39" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B40" s="22"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="24"/>
-      <c r="I40" s="24"/>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-      <c r="N40" s="24"/>
-      <c r="O40" s="24"/>
-      <c r="P40" s="24"/>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
-      <c r="U40" s="24"/>
-      <c r="V40" s="24"/>
-      <c r="W40" s="24"/>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="24"/>
-      <c r="Z40" s="24"/>
-      <c r="AA40" s="24"/>
-      <c r="AB40" s="24"/>
-      <c r="AC40" s="24"/>
-      <c r="AD40" s="25"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="17"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="17"/>
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="17"/>
+      <c r="AA40" s="17"/>
+      <c r="AB40" s="17"/>
+      <c r="AC40" s="17"/>
+      <c r="AD40" s="18"/>
     </row>
     <row r="41" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B41" s="26"/>
-      <c r="C41" s="3" t="s">
+      <c r="B41" s="19"/>
+      <c r="C41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3" t="s">
+      <c r="D41" s="1"/>
+      <c r="E41" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3" t="s">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3" t="s">
+      <c r="H41" s="1"/>
+      <c r="I41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3" t="s">
+      <c r="J41" s="1"/>
+      <c r="K41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3" t="s">
+      <c r="L41" s="1"/>
+      <c r="M41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3" t="s">
+      <c r="N41" s="1"/>
+      <c r="O41" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3" t="s">
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3" t="s">
+      <c r="R41" s="1"/>
+      <c r="S41" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3" t="s">
+      <c r="T41" s="1"/>
+      <c r="U41" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3" t="s">
+      <c r="V41" s="1"/>
+      <c r="W41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3" t="s">
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3" t="s">
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AB41" s="2"/>
-      <c r="AC41" s="3" t="s">
+      <c r="AC41" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AD41" s="28"/>
+      <c r="AD41" s="20"/>
     </row>
     <row r="42" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="26"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="2"/>
-      <c r="T42" s="2"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="2"/>
-      <c r="W42" s="2"/>
-      <c r="X42" s="2"/>
-      <c r="Y42" s="2"/>
-      <c r="Z42" s="2"/>
-      <c r="AA42" s="2"/>
-      <c r="AB42" s="2"/>
-      <c r="AC42" s="2"/>
-      <c r="AD42" s="28"/>
+      <c r="B42" s="19"/>
+      <c r="AD42" s="20"/>
     </row>
     <row r="43" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="B43" s="26"/>
-      <c r="C43" s="11" t="s">
+      <c r="B43" s="19"/>
+      <c r="C43" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J43" s="2"/>
-      <c r="K43" s="11" t="s">
+      <c r="K43" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="11" t="s">
+      <c r="M43" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="11" t="s">
+      <c r="O43" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="11" t="s">
+      <c r="Q43" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="R43" s="2"/>
-      <c r="S43" s="11" t="s">
+      <c r="S43" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="T43" s="2"/>
-      <c r="U43" s="11" t="s">
+      <c r="U43" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="V43" s="2"/>
-      <c r="W43" s="11" t="s">
+      <c r="W43" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="X43" s="2"/>
-      <c r="Y43" s="11" t="s">
+      <c r="Y43" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="Z43" s="2"/>
-      <c r="AA43" s="11" t="s">
+      <c r="AA43" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="AB43" s="2"/>
-      <c r="AC43" s="8" t="s">
+      <c r="AC43" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="AD43" s="28"/>
+      <c r="AD43" s="20"/>
     </row>
     <row r="44" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="26"/>
-      <c r="C44" s="9" t="s">
+      <c r="B44" s="19"/>
+      <c r="C44" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="H44" s="2"/>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J44" s="2"/>
-      <c r="K44" s="9" t="s">
+      <c r="K44" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="9" t="s">
+      <c r="M44" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="9" t="s">
+      <c r="O44" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="9" t="s">
+      <c r="Q44" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="R44" s="2"/>
-      <c r="S44" s="9" t="s">
+      <c r="S44" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="T44" s="2"/>
-      <c r="U44" s="9" t="s">
+      <c r="U44" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="V44" s="2"/>
-      <c r="W44" s="9" t="s">
+      <c r="W44" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="X44" s="2"/>
-      <c r="Y44" s="9" t="s">
+      <c r="Y44" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="Z44" s="2"/>
-      <c r="AA44" s="9" t="s">
+      <c r="AA44" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="AB44" s="2"/>
-      <c r="AC44" s="10" t="s">
+      <c r="AC44" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AD44" s="28"/>
+      <c r="AD44" s="20"/>
     </row>
     <row r="45" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="26"/>
-      <c r="C45" s="10" t="s">
+      <c r="B45" s="19"/>
+      <c r="C45" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H45" s="2"/>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J45" s="2"/>
-      <c r="K45" s="9" t="s">
+      <c r="K45" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="9" t="s">
+      <c r="M45" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="9" t="s">
+      <c r="O45" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="9" t="s">
+      <c r="Q45" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="R45" s="2"/>
-      <c r="S45" s="12" t="s">
+      <c r="S45" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="T45" s="2"/>
-      <c r="U45" s="9" t="s">
+      <c r="U45" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="V45" s="2"/>
-      <c r="W45" s="9" t="s">
+      <c r="W45" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="X45" s="2"/>
-      <c r="Y45" s="9" t="s">
+      <c r="Y45" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="Z45" s="2"/>
-      <c r="AA45" s="10" t="s">
+      <c r="AA45" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AB45" s="2"/>
-      <c r="AC45" s="2"/>
-      <c r="AD45" s="28"/>
+      <c r="AD45" s="20"/>
     </row>
     <row r="46" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="26"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="9" t="s">
+      <c r="B46" s="19"/>
+      <c r="E46" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J46" s="2"/>
-      <c r="K46" s="9" t="s">
+      <c r="K46" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="9" t="s">
+      <c r="M46" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="9" t="s">
+      <c r="O46" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="13" t="s">
+      <c r="Q46" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="R46" s="2"/>
-      <c r="S46" s="13" t="s">
+      <c r="S46" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="T46" s="2"/>
-      <c r="U46" s="9" t="s">
+      <c r="U46" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="V46" s="2"/>
-      <c r="W46" s="9" t="s">
+      <c r="W46" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="X46" s="2"/>
-      <c r="Y46" s="13" t="s">
+      <c r="Y46" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2"/>
-      <c r="AB46" s="2"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="28"/>
+      <c r="AD46" s="20"/>
     </row>
     <row r="47" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="26"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="10" t="s">
+      <c r="B47" s="19"/>
+      <c r="E47" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H47" s="2"/>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="9" t="s">
+      <c r="K47" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="9" t="s">
+      <c r="M47" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="9" t="s">
+      <c r="O47" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="2"/>
-      <c r="T47" s="2"/>
-      <c r="U47" s="9" t="s">
+      <c r="U47" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="V47" s="2"/>
-      <c r="W47" s="12" t="s">
+      <c r="W47" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="X47" s="2"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="2"/>
-      <c r="AA47" s="2"/>
-      <c r="AB47" s="2"/>
-      <c r="AC47" s="2"/>
-      <c r="AD47" s="28"/>
+      <c r="AD47" s="20"/>
     </row>
     <row r="48" spans="2:30" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="26"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="9" t="s">
+      <c r="B48" s="19"/>
+      <c r="G48" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="10" t="s">
+      <c r="K48" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="9" t="s">
+      <c r="M48" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="9" t="s">
+      <c r="O48" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="2"/>
-      <c r="T48" s="2"/>
-      <c r="U48" s="9" t="s">
+      <c r="U48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="V48" s="2"/>
-      <c r="W48" s="13" t="s">
+      <c r="W48" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="X48" s="2"/>
-      <c r="Y48" s="2"/>
-      <c r="Z48" s="2"/>
-      <c r="AA48" s="2"/>
-      <c r="AB48" s="2"/>
-      <c r="AC48" s="2"/>
-      <c r="AD48" s="28"/>
+      <c r="AD48" s="20"/>
     </row>
     <row r="49" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="26"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="9" t="s">
+      <c r="B49" s="19"/>
+      <c r="G49" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="10" t="s">
+      <c r="M49" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="10" t="s">
+      <c r="O49" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
-      <c r="T49" s="2"/>
-      <c r="U49" s="12" t="s">
+      <c r="U49" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="V49" s="2"/>
-      <c r="W49" s="2"/>
-      <c r="X49" s="2"/>
-      <c r="Y49" s="2"/>
-      <c r="Z49" s="2"/>
-      <c r="AA49" s="2"/>
-      <c r="AB49" s="2"/>
-      <c r="AC49" s="2"/>
-      <c r="AD49" s="28"/>
+      <c r="AD49" s="20"/>
     </row>
     <row r="50" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="26"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="9" t="s">
+      <c r="B50" s="19"/>
+      <c r="G50" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="14" t="s">
+      <c r="K50" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="2"/>
-      <c r="T50" s="2"/>
-      <c r="U50" s="13" t="s">
+      <c r="U50" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="V50" s="2"/>
-      <c r="W50" s="2"/>
-      <c r="X50" s="2"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="2"/>
-      <c r="AA50" s="2"/>
-      <c r="AB50" s="2"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="28"/>
+      <c r="AD50" s="20"/>
     </row>
     <row r="51" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B51" s="26"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="9" t="s">
+      <c r="B51" s="19"/>
+      <c r="G51" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="2"/>
-      <c r="AA51" s="2"/>
-      <c r="AB51" s="2"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="28"/>
+      <c r="AD51" s="20"/>
     </row>
     <row r="52" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B52" s="26"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="9" t="s">
+      <c r="B52" s="19"/>
+      <c r="G52" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="2"/>
-      <c r="T52" s="2"/>
-      <c r="U52" s="2"/>
-      <c r="V52" s="2"/>
-      <c r="W52" s="2"/>
-      <c r="X52" s="2"/>
-      <c r="Y52" s="2"/>
-      <c r="Z52" s="2"/>
-      <c r="AA52" s="2"/>
-      <c r="AB52" s="2"/>
-      <c r="AC52" s="2"/>
-      <c r="AD52" s="28"/>
+      <c r="AD52" s="20"/>
     </row>
     <row r="53" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B53" s="26"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="9" t="s">
+      <c r="B53" s="19"/>
+      <c r="G53" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="2"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="2"/>
-      <c r="X53" s="2"/>
-      <c r="Y53" s="2"/>
-      <c r="Z53" s="2"/>
-      <c r="AA53" s="2"/>
-      <c r="AB53" s="2"/>
-      <c r="AC53" s="2"/>
-      <c r="AD53" s="28"/>
+      <c r="AD53" s="20"/>
     </row>
     <row r="54" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="26"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="10" t="s">
+      <c r="B54" s="19"/>
+      <c r="G54" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" s="2"/>
-      <c r="Q54" s="2"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="2"/>
-      <c r="T54" s="2"/>
-      <c r="U54" s="2"/>
-      <c r="V54" s="2"/>
-      <c r="W54" s="2"/>
-      <c r="X54" s="2"/>
-      <c r="Y54" s="2"/>
-      <c r="Z54" s="2"/>
-      <c r="AA54" s="2"/>
-      <c r="AB54" s="2"/>
-      <c r="AC54" s="2"/>
-      <c r="AD54" s="28"/>
+      <c r="AD54" s="20"/>
     </row>
     <row r="55" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="30"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
-      <c r="M55" s="32"/>
-      <c r="N55" s="32"/>
-      <c r="O55" s="32"/>
-      <c r="P55" s="32"/>
-      <c r="Q55" s="32"/>
-      <c r="R55" s="32"/>
-      <c r="S55" s="32"/>
-      <c r="T55" s="32"/>
-      <c r="U55" s="32"/>
-      <c r="V55" s="32"/>
-      <c r="W55" s="32"/>
-      <c r="X55" s="32"/>
-      <c r="Y55" s="32"/>
-      <c r="Z55" s="32"/>
-      <c r="AA55" s="32"/>
-      <c r="AB55" s="32"/>
-      <c r="AC55" s="32"/>
-      <c r="AD55" s="33"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="23"/>
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="23"/>
+      <c r="L55" s="23"/>
+      <c r="M55" s="23"/>
+      <c r="N55" s="23"/>
+      <c r="O55" s="23"/>
+      <c r="P55" s="23"/>
+      <c r="Q55" s="23"/>
+      <c r="R55" s="23"/>
+      <c r="S55" s="23"/>
+      <c r="T55" s="23"/>
+      <c r="U55" s="23"/>
+      <c r="V55" s="23"/>
+      <c r="W55" s="23"/>
+      <c r="X55" s="23"/>
+      <c r="Y55" s="23"/>
+      <c r="Z55" s="23"/>
+      <c r="AA55" s="23"/>
+      <c r="AB55" s="23"/>
+      <c r="AC55" s="23"/>
+      <c r="AD55" s="24"/>
     </row>
     <row r="58" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="9" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="59" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="16"/>
-      <c r="O59" s="16"/>
-      <c r="P59" s="16"/>
-      <c r="Q59" s="16"/>
-      <c r="R59" s="16"/>
-      <c r="S59" s="16"/>
-      <c r="T59" s="16"/>
-      <c r="U59" s="16"/>
-      <c r="V59" s="16"/>
-      <c r="W59" s="16"/>
-      <c r="X59" s="16"/>
-      <c r="Y59" s="16"/>
-      <c r="Z59" s="16"/>
-      <c r="AA59" s="16"/>
-      <c r="AB59" s="16"/>
-      <c r="AC59" s="16"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
+      <c r="V59" s="10"/>
+      <c r="W59" s="10"/>
+      <c r="X59" s="10"/>
+      <c r="Y59" s="10"/>
+      <c r="Z59" s="10"/>
+      <c r="AA59" s="10"/>
+      <c r="AB59" s="10"/>
+      <c r="AC59" s="10"/>
     </row>
     <row r="60" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B60" s="22"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="23"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="23"/>
-      <c r="J60" s="23"/>
-      <c r="K60" s="23"/>
-      <c r="L60" s="23"/>
-      <c r="M60" s="23"/>
-      <c r="N60" s="23"/>
-      <c r="O60" s="23"/>
-      <c r="P60" s="23"/>
-      <c r="Q60" s="23"/>
-      <c r="R60" s="23"/>
-      <c r="S60" s="23"/>
-      <c r="T60" s="23"/>
-      <c r="U60" s="23"/>
-      <c r="V60" s="23"/>
-      <c r="W60" s="23"/>
-      <c r="X60" s="23"/>
-      <c r="Y60" s="23"/>
-      <c r="Z60" s="23"/>
-      <c r="AA60" s="23"/>
-      <c r="AB60" s="23"/>
-      <c r="AC60" s="23"/>
-      <c r="AD60" s="24"/>
-      <c r="AE60" s="24"/>
-      <c r="AF60" s="24"/>
-      <c r="AG60" s="24"/>
-      <c r="AH60" s="25"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
+      <c r="N60" s="16"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="16"/>
+      <c r="Q60" s="16"/>
+      <c r="R60" s="16"/>
+      <c r="S60" s="16"/>
+      <c r="T60" s="16"/>
+      <c r="U60" s="16"/>
+      <c r="V60" s="16"/>
+      <c r="W60" s="16"/>
+      <c r="X60" s="16"/>
+      <c r="Y60" s="16"/>
+      <c r="Z60" s="16"/>
+      <c r="AA60" s="16"/>
+      <c r="AB60" s="16"/>
+      <c r="AC60" s="16"/>
+      <c r="AD60" s="17"/>
+      <c r="AE60" s="17"/>
+      <c r="AF60" s="17"/>
+      <c r="AG60" s="17"/>
+      <c r="AH60" s="18"/>
     </row>
     <row r="61" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B61" s="26"/>
-      <c r="C61" s="27" t="s">
+      <c r="B61" s="19"/>
+      <c r="C61" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27" t="s">
+      <c r="D61" s="9"/>
+      <c r="E61" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27" t="s">
+      <c r="F61" s="9"/>
+      <c r="G61" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27" t="s">
+      <c r="H61" s="9"/>
+      <c r="I61" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27" t="s">
+      <c r="J61" s="9"/>
+      <c r="K61" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27" t="s">
+      <c r="L61" s="9"/>
+      <c r="M61" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27" t="s">
+      <c r="N61" s="9"/>
+      <c r="O61" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27" t="s">
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27" t="s">
+      <c r="R61" s="9"/>
+      <c r="S61" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27" t="s">
+      <c r="T61" s="9"/>
+      <c r="U61" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27" t="s">
+      <c r="V61" s="9"/>
+      <c r="W61" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X61" s="27"/>
-      <c r="Y61" s="27" t="s">
+      <c r="X61" s="9"/>
+      <c r="Y61" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="Z61" s="27"/>
-      <c r="AA61" s="27" t="s">
+      <c r="Z61" s="9"/>
+      <c r="AA61" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AB61" s="21"/>
-      <c r="AC61" s="27" t="s">
+      <c r="AB61" s="10"/>
+      <c r="AC61" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="AD61" s="2"/>
-      <c r="AE61" s="3" t="s">
+      <c r="AE61" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AF61" s="2"/>
-      <c r="AG61" s="3" t="s">
+      <c r="AG61" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AH61" s="28"/>
+      <c r="AH61" s="20"/>
     </row>
     <row r="62" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="26"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
-      <c r="L62" s="21"/>
-      <c r="M62" s="21"/>
-      <c r="N62" s="21"/>
-      <c r="O62" s="21"/>
-      <c r="P62" s="21"/>
-      <c r="Q62" s="21"/>
-      <c r="R62" s="21"/>
-      <c r="S62" s="21"/>
-      <c r="T62" s="21"/>
-      <c r="U62" s="21"/>
-      <c r="V62" s="21"/>
-      <c r="W62" s="21"/>
-      <c r="X62" s="21"/>
-      <c r="Y62" s="21"/>
-      <c r="Z62" s="21"/>
-      <c r="AA62" s="21"/>
-      <c r="AB62" s="21"/>
-      <c r="AC62" s="21"/>
-      <c r="AD62" s="2"/>
-      <c r="AE62" s="2"/>
-      <c r="AF62" s="2"/>
-      <c r="AG62" s="2"/>
-      <c r="AH62" s="28"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="10"/>
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+      <c r="K62" s="10"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
+      <c r="S62" s="10"/>
+      <c r="T62" s="10"/>
+      <c r="U62" s="10"/>
+      <c r="V62" s="10"/>
+      <c r="W62" s="10"/>
+      <c r="X62" s="10"/>
+      <c r="Y62" s="10"/>
+      <c r="Z62" s="10"/>
+      <c r="AA62" s="10"/>
+      <c r="AB62" s="10"/>
+      <c r="AC62" s="10"/>
+      <c r="AH62" s="20"/>
     </row>
     <row r="63" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B63" s="26"/>
-      <c r="C63" s="17" t="s">
+      <c r="B63" s="19"/>
+      <c r="C63" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D63" s="21"/>
-      <c r="E63" s="17" t="s">
+      <c r="D63" s="10"/>
+      <c r="E63" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F63" s="21"/>
-      <c r="G63" s="17" t="s">
+      <c r="F63" s="10"/>
+      <c r="G63" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="H63" s="21"/>
-      <c r="I63" s="17" t="s">
+      <c r="H63" s="10"/>
+      <c r="I63" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J63" s="21"/>
-      <c r="K63" s="17" t="s">
+      <c r="J63" s="10"/>
+      <c r="K63" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="L63" s="21"/>
-      <c r="M63" s="17" t="s">
+      <c r="L63" s="10"/>
+      <c r="M63" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="N63" s="21"/>
-      <c r="O63" s="17" t="s">
+      <c r="N63" s="10"/>
+      <c r="O63" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="17" t="s">
+      <c r="P63" s="10"/>
+      <c r="Q63" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="R63" s="21"/>
-      <c r="S63" s="17" t="s">
+      <c r="R63" s="10"/>
+      <c r="S63" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="T63" s="21"/>
-      <c r="U63" s="17" t="s">
+      <c r="T63" s="10"/>
+      <c r="U63" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="V63" s="21"/>
-      <c r="W63" s="17" t="s">
+      <c r="V63" s="10"/>
+      <c r="W63" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="X63" s="21"/>
-      <c r="Y63" s="17" t="s">
+      <c r="X63" s="10"/>
+      <c r="Y63" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="Z63" s="21"/>
-      <c r="AA63" s="17" t="s">
+      <c r="Z63" s="10"/>
+      <c r="AA63" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="AB63" s="21"/>
-      <c r="AC63" s="18" t="s">
+      <c r="AB63" s="10"/>
+      <c r="AC63" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="AD63" s="2"/>
-      <c r="AE63" s="11" t="s">
+      <c r="AE63" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="AF63" s="2"/>
-      <c r="AG63" s="11" t="s">
+      <c r="AG63" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="AH63" s="28"/>
+      <c r="AH63" s="20"/>
     </row>
     <row r="64" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="26"/>
-      <c r="C64" s="19" t="s">
+      <c r="B64" s="19"/>
+      <c r="C64" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D64" s="21"/>
-      <c r="E64" s="19" t="s">
+      <c r="D64" s="10"/>
+      <c r="E64" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F64" s="21"/>
-      <c r="G64" s="19" t="s">
+      <c r="F64" s="10"/>
+      <c r="G64" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="H64" s="21"/>
-      <c r="I64" s="19" t="s">
+      <c r="H64" s="10"/>
+      <c r="I64" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J64" s="21"/>
-      <c r="K64" s="19" t="s">
+      <c r="J64" s="10"/>
+      <c r="K64" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="L64" s="21"/>
-      <c r="M64" s="19" t="s">
+      <c r="L64" s="10"/>
+      <c r="M64" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="N64" s="21"/>
-      <c r="O64" s="19" t="s">
+      <c r="N64" s="10"/>
+      <c r="O64" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="P64" s="21"/>
-      <c r="Q64" s="19" t="s">
+      <c r="P64" s="10"/>
+      <c r="Q64" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="R64" s="21"/>
-      <c r="S64" s="19" t="s">
+      <c r="R64" s="10"/>
+      <c r="S64" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="T64" s="21"/>
-      <c r="U64" s="19" t="s">
+      <c r="T64" s="10"/>
+      <c r="U64" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="V64" s="21"/>
-      <c r="W64" s="19" t="s">
+      <c r="V64" s="10"/>
+      <c r="W64" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="X64" s="21"/>
-      <c r="Y64" s="19" t="s">
+      <c r="X64" s="10"/>
+      <c r="Y64" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="Z64" s="21"/>
-      <c r="AA64" s="19" t="s">
+      <c r="Z64" s="10"/>
+      <c r="AA64" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AB64" s="21"/>
-      <c r="AC64" s="20" t="s">
+      <c r="AB64" s="10"/>
+      <c r="AC64" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AD64" s="2"/>
-      <c r="AE64" s="10" t="s">
+      <c r="AE64" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="AF64" s="2"/>
-      <c r="AG64" s="9" t="s">
+      <c r="AG64" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="AH64" s="28"/>
+      <c r="AH64" s="20"/>
     </row>
     <row r="65" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="26"/>
-      <c r="C65" s="20" t="s">
+      <c r="B65" s="19"/>
+      <c r="C65" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D65" s="21"/>
-      <c r="E65" s="19" t="s">
+      <c r="D65" s="10"/>
+      <c r="E65" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="F65" s="21"/>
-      <c r="G65" s="19" t="s">
+      <c r="F65" s="10"/>
+      <c r="G65" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="H65" s="21"/>
-      <c r="I65" s="19" t="s">
+      <c r="H65" s="10"/>
+      <c r="I65" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="J65" s="21"/>
-      <c r="K65" s="19" t="s">
+      <c r="J65" s="10"/>
+      <c r="K65" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="L65" s="21"/>
-      <c r="M65" s="19" t="s">
+      <c r="L65" s="10"/>
+      <c r="M65" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="N65" s="21"/>
-      <c r="O65" s="19" t="s">
+      <c r="N65" s="10"/>
+      <c r="O65" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="P65" s="21"/>
-      <c r="Q65" s="19" t="s">
+      <c r="P65" s="10"/>
+      <c r="Q65" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="R65" s="21"/>
-      <c r="S65" s="19" t="s">
+      <c r="R65" s="10"/>
+      <c r="S65" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="T65" s="21"/>
-      <c r="U65" s="19" t="s">
+      <c r="T65" s="10"/>
+      <c r="U65" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="V65" s="21"/>
-      <c r="W65" s="19" t="s">
+      <c r="V65" s="10"/>
+      <c r="W65" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="X65" s="21"/>
-      <c r="Y65" s="19" t="s">
+      <c r="X65" s="10"/>
+      <c r="Y65" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Z65" s="21"/>
-      <c r="AA65" s="20" t="s">
+      <c r="Z65" s="10"/>
+      <c r="AA65" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="AB65" s="21"/>
-      <c r="AC65" s="21"/>
-      <c r="AD65" s="2"/>
-      <c r="AE65" s="2"/>
-      <c r="AF65" s="2"/>
-      <c r="AG65" s="9" t="s">
+      <c r="AB65" s="10"/>
+      <c r="AC65" s="10"/>
+      <c r="AG65" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="AH65" s="28"/>
+      <c r="AH65" s="20"/>
     </row>
     <row r="66" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="26"/>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="19" t="s">
+      <c r="B66" s="19"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F66" s="21"/>
-      <c r="G66" s="19" t="s">
+      <c r="F66" s="10"/>
+      <c r="G66" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H66" s="21"/>
-      <c r="I66" s="19" t="s">
+      <c r="H66" s="10"/>
+      <c r="I66" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J66" s="21"/>
-      <c r="K66" s="19" t="s">
+      <c r="J66" s="10"/>
+      <c r="K66" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="L66" s="21"/>
-      <c r="M66" s="19" t="s">
+      <c r="L66" s="10"/>
+      <c r="M66" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="N66" s="21"/>
-      <c r="O66" s="19" t="s">
+      <c r="N66" s="10"/>
+      <c r="O66" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="P66" s="21"/>
-      <c r="Q66" s="20" t="s">
+      <c r="P66" s="10"/>
+      <c r="Q66" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="R66" s="21"/>
-      <c r="S66" s="20" t="s">
+      <c r="R66" s="10"/>
+      <c r="S66" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="T66" s="21"/>
-      <c r="U66" s="19" t="s">
+      <c r="T66" s="10"/>
+      <c r="U66" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="V66" s="21"/>
-      <c r="W66" s="19" t="s">
+      <c r="V66" s="10"/>
+      <c r="W66" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="X66" s="21"/>
-      <c r="Y66" s="20" t="s">
+      <c r="X66" s="10"/>
+      <c r="Y66" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="Z66" s="21"/>
-      <c r="AA66" s="21"/>
-      <c r="AB66" s="21"/>
-      <c r="AC66" s="21"/>
-      <c r="AD66" s="2"/>
-      <c r="AE66" s="2"/>
-      <c r="AF66" s="2"/>
-      <c r="AG66" s="9" t="s">
+      <c r="Z66" s="10"/>
+      <c r="AA66" s="10"/>
+      <c r="AB66" s="10"/>
+      <c r="AC66" s="10"/>
+      <c r="AG66" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="AH66" s="28"/>
+      <c r="AH66" s="20"/>
     </row>
     <row r="67" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="26"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
-      <c r="E67" s="20" t="s">
+      <c r="B67" s="19"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="F67" s="21"/>
-      <c r="G67" s="19" t="s">
+      <c r="F67" s="10"/>
+      <c r="G67" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="H67" s="21"/>
-      <c r="I67" s="20" t="s">
+      <c r="H67" s="10"/>
+      <c r="I67" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J67" s="21"/>
-      <c r="K67" s="19" t="s">
+      <c r="J67" s="10"/>
+      <c r="K67" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="L67" s="21"/>
-      <c r="M67" s="19" t="s">
+      <c r="L67" s="10"/>
+      <c r="M67" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="N67" s="21"/>
-      <c r="O67" s="19" t="s">
+      <c r="N67" s="10"/>
+      <c r="O67" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="P67" s="21"/>
-      <c r="Q67" s="21"/>
-      <c r="R67" s="21"/>
-      <c r="S67" s="21"/>
-      <c r="T67" s="21"/>
-      <c r="U67" s="19" t="s">
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
+      <c r="S67" s="10"/>
+      <c r="T67" s="10"/>
+      <c r="U67" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="V67" s="21"/>
-      <c r="W67" s="19" t="s">
+      <c r="V67" s="10"/>
+      <c r="W67" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="X67" s="21"/>
-      <c r="Y67" s="21"/>
-      <c r="Z67" s="21"/>
-      <c r="AA67" s="21"/>
-      <c r="AB67" s="21"/>
-      <c r="AC67" s="21"/>
-      <c r="AD67" s="2"/>
-      <c r="AE67" s="2"/>
-      <c r="AF67" s="2"/>
-      <c r="AG67" s="9" t="s">
+      <c r="X67" s="10"/>
+      <c r="Y67" s="10"/>
+      <c r="Z67" s="10"/>
+      <c r="AA67" s="10"/>
+      <c r="AB67" s="10"/>
+      <c r="AC67" s="10"/>
+      <c r="AG67" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="AH67" s="28"/>
+      <c r="AH67" s="20"/>
     </row>
     <row r="68" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="26"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="19" t="s">
+      <c r="B68" s="19"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="20" t="s">
+      <c r="H68" s="10"/>
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+      <c r="K68" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="L68" s="21"/>
-      <c r="M68" s="19" t="s">
+      <c r="L68" s="10"/>
+      <c r="M68" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="N68" s="21"/>
-      <c r="O68" s="19" t="s">
+      <c r="N68" s="10"/>
+      <c r="O68" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="P68" s="21"/>
-      <c r="Q68" s="21"/>
-      <c r="R68" s="21"/>
-      <c r="S68" s="21"/>
-      <c r="T68" s="21"/>
-      <c r="U68" s="19" t="s">
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
+      <c r="S68" s="10"/>
+      <c r="T68" s="10"/>
+      <c r="U68" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="V68" s="21"/>
-      <c r="W68" s="20" t="s">
+      <c r="V68" s="10"/>
+      <c r="W68" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="X68" s="21"/>
-      <c r="Y68" s="21"/>
-      <c r="Z68" s="21"/>
-      <c r="AA68" s="21"/>
-      <c r="AB68" s="21"/>
-      <c r="AC68" s="21"/>
-      <c r="AD68" s="2"/>
-      <c r="AE68" s="2"/>
-      <c r="AF68" s="2"/>
-      <c r="AG68" s="10" t="s">
+      <c r="X68" s="10"/>
+      <c r="Y68" s="10"/>
+      <c r="Z68" s="10"/>
+      <c r="AA68" s="10"/>
+      <c r="AB68" s="10"/>
+      <c r="AC68" s="10"/>
+      <c r="AG68" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AH68" s="28"/>
+      <c r="AH68" s="20"/>
     </row>
     <row r="69" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="26"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="19" t="s">
+      <c r="B69" s="19"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="21"/>
-      <c r="M69" s="20" t="s">
+      <c r="H69" s="10"/>
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+      <c r="K69" s="10"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="N69" s="21"/>
-      <c r="O69" s="20" t="s">
+      <c r="N69" s="10"/>
+      <c r="O69" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="P69" s="21"/>
-      <c r="Q69" s="21"/>
-      <c r="R69" s="21"/>
-      <c r="S69" s="21"/>
-      <c r="T69" s="21"/>
-      <c r="U69" s="19" t="s">
+      <c r="P69" s="10"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="V69" s="21"/>
-      <c r="W69" s="21"/>
-      <c r="X69" s="21"/>
-      <c r="Y69" s="21"/>
-      <c r="Z69" s="21"/>
-      <c r="AA69" s="21"/>
-      <c r="AB69" s="21"/>
-      <c r="AC69" s="21"/>
-      <c r="AD69" s="2"/>
-      <c r="AE69" s="2"/>
-      <c r="AF69" s="2"/>
-      <c r="AG69" s="2"/>
-      <c r="AH69" s="28"/>
+      <c r="V69" s="10"/>
+      <c r="W69" s="10"/>
+      <c r="X69" s="10"/>
+      <c r="Y69" s="10"/>
+      <c r="Z69" s="10"/>
+      <c r="AA69" s="10"/>
+      <c r="AB69" s="10"/>
+      <c r="AC69" s="10"/>
+      <c r="AH69" s="20"/>
     </row>
     <row r="70" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="26"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="20" t="s">
+      <c r="B70" s="19"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
-      <c r="P70" s="21"/>
-      <c r="Q70" s="21"/>
-      <c r="R70" s="21"/>
-      <c r="S70" s="21"/>
-      <c r="T70" s="21"/>
-      <c r="U70" s="20" t="s">
+      <c r="H70" s="10"/>
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
+      <c r="S70" s="10"/>
+      <c r="T70" s="10"/>
+      <c r="U70" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="V70" s="21"/>
-      <c r="W70" s="21"/>
-      <c r="X70" s="21"/>
-      <c r="Y70" s="21"/>
-      <c r="Z70" s="21"/>
-      <c r="AA70" s="21"/>
-      <c r="AB70" s="21"/>
-      <c r="AC70" s="21"/>
-      <c r="AD70" s="2"/>
-      <c r="AE70" s="2"/>
-      <c r="AF70" s="2"/>
-      <c r="AG70" s="2"/>
-      <c r="AH70" s="28"/>
+      <c r="V70" s="10"/>
+      <c r="W70" s="10"/>
+      <c r="X70" s="10"/>
+      <c r="Y70" s="10"/>
+      <c r="Z70" s="10"/>
+      <c r="AA70" s="10"/>
+      <c r="AB70" s="10"/>
+      <c r="AC70" s="10"/>
+      <c r="AH70" s="20"/>
     </row>
     <row r="71" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B71" s="26"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
-      <c r="P71" s="21"/>
-      <c r="Q71" s="21"/>
-      <c r="R71" s="21"/>
-      <c r="S71" s="21"/>
-      <c r="T71" s="21"/>
-      <c r="U71" s="21"/>
-      <c r="V71" s="21"/>
-      <c r="W71" s="21"/>
-      <c r="X71" s="21"/>
-      <c r="Y71" s="21"/>
-      <c r="Z71" s="21"/>
-      <c r="AA71" s="21"/>
-      <c r="AB71" s="21"/>
-      <c r="AC71" s="21"/>
-      <c r="AD71" s="2"/>
-      <c r="AE71" s="2"/>
-      <c r="AF71" s="2"/>
-      <c r="AG71" s="2"/>
-      <c r="AH71" s="28"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="10"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
+      <c r="V71" s="10"/>
+      <c r="W71" s="10"/>
+      <c r="X71" s="10"/>
+      <c r="Y71" s="10"/>
+      <c r="Z71" s="10"/>
+      <c r="AA71" s="10"/>
+      <c r="AB71" s="10"/>
+      <c r="AC71" s="10"/>
+      <c r="AH71" s="20"/>
     </row>
     <row r="72" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B72" s="26"/>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="29" t="s">
+      <c r="B72" s="19"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
-      <c r="P72" s="21"/>
-      <c r="Q72" s="21"/>
-      <c r="R72" s="21"/>
-      <c r="S72" s="21"/>
-      <c r="T72" s="21"/>
-      <c r="U72" s="21"/>
-      <c r="V72" s="21"/>
-      <c r="W72" s="21"/>
-      <c r="X72" s="21"/>
-      <c r="Y72" s="21"/>
-      <c r="Z72" s="21"/>
-      <c r="AA72" s="21"/>
-      <c r="AB72" s="21"/>
-      <c r="AC72" s="21"/>
-      <c r="AD72" s="2"/>
-      <c r="AE72" s="2"/>
-      <c r="AF72" s="2"/>
-      <c r="AG72" s="2"/>
-      <c r="AH72" s="28"/>
+      <c r="H72" s="10"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
+      <c r="S72" s="10"/>
+      <c r="T72" s="10"/>
+      <c r="U72" s="10"/>
+      <c r="V72" s="10"/>
+      <c r="W72" s="10"/>
+      <c r="X72" s="10"/>
+      <c r="Y72" s="10"/>
+      <c r="Z72" s="10"/>
+      <c r="AA72" s="10"/>
+      <c r="AB72" s="10"/>
+      <c r="AC72" s="10"/>
+      <c r="AH72" s="20"/>
     </row>
     <row r="73" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="B73" s="26"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="29" t="s">
+      <c r="B73" s="19"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
-      <c r="P73" s="21"/>
-      <c r="Q73" s="21"/>
-      <c r="R73" s="21"/>
-      <c r="S73" s="21"/>
-      <c r="T73" s="21"/>
-      <c r="U73" s="21"/>
-      <c r="V73" s="21"/>
-      <c r="W73" s="21"/>
-      <c r="X73" s="21"/>
-      <c r="Y73" s="21"/>
-      <c r="Z73" s="21"/>
-      <c r="AA73" s="21"/>
-      <c r="AB73" s="21"/>
-      <c r="AC73" s="21"/>
-      <c r="AD73" s="2"/>
-      <c r="AE73" s="2"/>
-      <c r="AF73" s="2"/>
-      <c r="AG73" s="2"/>
-      <c r="AH73" s="28"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="10"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
+      <c r="V73" s="10"/>
+      <c r="W73" s="10"/>
+      <c r="X73" s="10"/>
+      <c r="Y73" s="10"/>
+      <c r="Z73" s="10"/>
+      <c r="AA73" s="10"/>
+      <c r="AB73" s="10"/>
+      <c r="AC73" s="10"/>
+      <c r="AH73" s="20"/>
     </row>
     <row r="74" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="30"/>
-      <c r="C74" s="31"/>
-      <c r="D74" s="31"/>
-      <c r="E74" s="31"/>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="31"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="31"/>
-      <c r="K74" s="31"/>
-      <c r="L74" s="31"/>
-      <c r="M74" s="31"/>
-      <c r="N74" s="31"/>
-      <c r="O74" s="31"/>
-      <c r="P74" s="31"/>
-      <c r="Q74" s="31"/>
-      <c r="R74" s="31"/>
-      <c r="S74" s="31"/>
-      <c r="T74" s="31"/>
-      <c r="U74" s="31"/>
-      <c r="V74" s="31"/>
-      <c r="W74" s="31"/>
-      <c r="X74" s="31"/>
-      <c r="Y74" s="31"/>
-      <c r="Z74" s="31"/>
-      <c r="AA74" s="31"/>
-      <c r="AB74" s="31"/>
-      <c r="AC74" s="31"/>
-      <c r="AD74" s="32"/>
-      <c r="AE74" s="32"/>
-      <c r="AF74" s="32"/>
-      <c r="AG74" s="32"/>
-      <c r="AH74" s="33"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="22"/>
+      <c r="L74" s="22"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="22"/>
+      <c r="P74" s="22"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="22"/>
+      <c r="S74" s="22"/>
+      <c r="T74" s="22"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="22"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="22"/>
+      <c r="Y74" s="22"/>
+      <c r="Z74" s="22"/>
+      <c r="AA74" s="22"/>
+      <c r="AB74" s="22"/>
+      <c r="AC74" s="22"/>
+      <c r="AD74" s="23"/>
+      <c r="AE74" s="23"/>
+      <c r="AF74" s="23"/>
+      <c r="AG74" s="23"/>
+      <c r="AH74" s="24"/>
     </row>
     <row r="75" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="H75" s="16"/>
-      <c r="I75" s="16"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="16"/>
-      <c r="O75" s="16"/>
-      <c r="P75" s="16"/>
-      <c r="Q75" s="16"/>
-      <c r="R75" s="16"/>
-      <c r="S75" s="16"/>
-      <c r="T75" s="16"/>
-      <c r="U75" s="16"/>
-      <c r="V75" s="16"/>
-      <c r="W75" s="16"/>
-      <c r="X75" s="16"/>
-      <c r="Y75" s="16"/>
-      <c r="Z75" s="16"/>
-      <c r="AA75" s="16"/>
-      <c r="AB75" s="16"/>
-      <c r="AC75" s="16"/>
+      <c r="C75" s="10"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="10"/>
+      <c r="H75" s="10"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="10"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
+      <c r="V75" s="10"/>
+      <c r="W75" s="10"/>
+      <c r="X75" s="10"/>
+      <c r="Y75" s="10"/>
+      <c r="Z75" s="10"/>
+      <c r="AA75" s="10"/>
+      <c r="AB75" s="10"/>
+      <c r="AC75" s="10"/>
     </row>
     <row r="76" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="H76" s="16"/>
-      <c r="I76" s="16"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="16"/>
-      <c r="O76" s="16"/>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="16"/>
-      <c r="R76" s="16"/>
-      <c r="S76" s="16"/>
-      <c r="T76" s="16"/>
-      <c r="U76" s="16"/>
-      <c r="V76" s="16"/>
-      <c r="W76" s="16"/>
-      <c r="X76" s="16"/>
-      <c r="Y76" s="16"/>
-      <c r="Z76" s="16"/>
-      <c r="AA76" s="16"/>
-      <c r="AB76" s="16"/>
-      <c r="AC76" s="16"/>
+      <c r="C76" s="10"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="10"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="10"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
+      <c r="S76" s="10"/>
+      <c r="T76" s="10"/>
+      <c r="U76" s="10"/>
+      <c r="V76" s="10"/>
+      <c r="W76" s="10"/>
+      <c r="X76" s="10"/>
+      <c r="Y76" s="10"/>
+      <c r="Z76" s="10"/>
+      <c r="AA76" s="10"/>
+      <c r="AB76" s="10"/>
+      <c r="AC76" s="10"/>
     </row>
     <row r="77" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="16"/>
-      <c r="O77" s="16"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="16"/>
-      <c r="R77" s="16"/>
-      <c r="S77" s="16"/>
-      <c r="T77" s="16"/>
-      <c r="U77" s="16"/>
-      <c r="V77" s="16"/>
-      <c r="W77" s="16"/>
-      <c r="X77" s="16"/>
-      <c r="Y77" s="16"/>
-      <c r="Z77" s="16"/>
-      <c r="AA77" s="16"/>
-      <c r="AB77" s="16"/>
-      <c r="AC77" s="16"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="10"/>
+      <c r="G77" s="10"/>
+      <c r="H77" s="10"/>
+      <c r="I77" s="10"/>
+      <c r="J77" s="10"/>
+      <c r="K77" s="10"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="10"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
+      <c r="V77" s="10"/>
+      <c r="W77" s="10"/>
+      <c r="X77" s="10"/>
+      <c r="Y77" s="10"/>
+      <c r="Z77" s="10"/>
+      <c r="AA77" s="10"/>
+      <c r="AB77" s="10"/>
+      <c r="AC77" s="10"/>
     </row>
     <row r="78" spans="2:34" x14ac:dyDescent="0.2">
-      <c r="P78" s="16"/>
-      <c r="Q78" s="16"/>
-      <c r="R78" s="16"/>
-      <c r="S78" s="16"/>
-      <c r="T78" s="16"/>
-      <c r="U78" s="16"/>
-      <c r="V78" s="16"/>
-      <c r="W78" s="16"/>
-      <c r="X78" s="16"/>
-      <c r="Y78" s="16"/>
-      <c r="Z78" s="16"/>
-      <c r="AA78" s="16"/>
-      <c r="AB78" s="16"/>
-      <c r="AC78" s="16"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
+      <c r="S78" s="10"/>
+      <c r="T78" s="10"/>
+      <c r="U78" s="10"/>
+      <c r="V78" s="10"/>
+      <c r="W78" s="10"/>
+      <c r="X78" s="10"/>
+      <c r="Y78" s="10"/>
+      <c r="Z78" s="10"/>
+      <c r="AA78" s="10"/>
+      <c r="AB78" s="10"/>
+      <c r="AC78" s="10"/>
     </row>
     <row r="81" spans="16:23" x14ac:dyDescent="0.2">
       <c r="P81" s="1"/>
@@ -3887,4 +3428,2497 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B909339B-2A5D-DA42-A22F-D0F9E736EAD4}">
+  <dimension ref="A1:AV54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="19" max="19" width="10.83203125" customWidth="1"/>
+    <col min="21" max="21" width="10.83203125" customWidth="1"/>
+    <col min="23" max="23" width="10.83203125" customWidth="1"/>
+    <col min="25" max="25" width="10.83203125" customWidth="1"/>
+    <col min="27" max="27" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AH1" s="1"/>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C3" s="19"/>
+      <c r="D3" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+    </row>
+    <row r="4" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="19"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+    </row>
+    <row r="5" spans="1:35" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="27"/>
+      <c r="H5" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="N5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AD5" s="29"/>
+    </row>
+    <row r="6" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="19"/>
+      <c r="D6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="28"/>
+      <c r="F6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="27"/>
+      <c r="H6" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="N6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AD6" s="28"/>
+    </row>
+    <row r="7" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="19"/>
+      <c r="D7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="20"/>
+      <c r="N7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AD7" s="28"/>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C8" s="19"/>
+      <c r="D8" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="20"/>
+      <c r="N8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="V8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AD8" s="28"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C9" s="19"/>
+      <c r="D9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="20"/>
+      <c r="N9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AD9" s="28"/>
+    </row>
+    <row r="10" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="19"/>
+      <c r="D10" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="20"/>
+      <c r="N10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="27"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="28"/>
+    </row>
+    <row r="11" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="21"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="N11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="V11" s="27"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+    </row>
+    <row r="12" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="V12" s="27"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+      <c r="N13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C14" s="19"/>
+      <c r="D14" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="28"/>
+    </row>
+    <row r="15" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="19"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="20"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="27"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+    </row>
+    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="28"/>
+      <c r="H16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="20"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28"/>
+      <c r="AH16"/>
+      <c r="AI16"/>
+    </row>
+    <row r="17" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="19"/>
+      <c r="D17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="28"/>
+      <c r="H17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="20"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="1"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="27"/>
+      <c r="AC17" s="27"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28"/>
+    </row>
+    <row r="18" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C18" s="19"/>
+      <c r="D18" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" s="20"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="27"/>
+      <c r="AB18" s="27"/>
+      <c r="AC18" s="27"/>
+      <c r="AD18" s="28"/>
+      <c r="AE18" s="28"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28"/>
+    </row>
+    <row r="19" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C19" s="19"/>
+      <c r="D19" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="20"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+    </row>
+    <row r="20" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C20" s="19"/>
+      <c r="D20" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="20"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+      <c r="AP20" s="1"/>
+      <c r="AQ20" s="1"/>
+      <c r="AR20" s="1"/>
+      <c r="AS20" s="1"/>
+      <c r="AT20" s="1"/>
+      <c r="AU20" s="1"/>
+      <c r="AV20" s="1"/>
+    </row>
+    <row r="21" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C21" s="19"/>
+      <c r="D21" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="20"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+    </row>
+    <row r="22" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="19"/>
+      <c r="D22" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="20"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+      <c r="AB22" s="10"/>
+      <c r="AC22" s="10"/>
+    </row>
+    <row r="23" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C23" s="19"/>
+      <c r="D23" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="20"/>
+    </row>
+    <row r="24" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="19"/>
+      <c r="D24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="20"/>
+    </row>
+    <row r="25" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="21"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="24"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+    </row>
+    <row r="26" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="18"/>
+    </row>
+    <row r="28" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C28" s="19"/>
+      <c r="D28" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="28"/>
+      <c r="H28" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" s="28"/>
+      <c r="J28" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="K28" s="36"/>
+    </row>
+    <row r="29" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="19"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="20"/>
+    </row>
+    <row r="30" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C30" s="19"/>
+      <c r="D30" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="28"/>
+      <c r="F30" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="28"/>
+      <c r="H30" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="I30" s="28"/>
+      <c r="J30" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K30" s="20"/>
+    </row>
+    <row r="31" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C31" s="19"/>
+      <c r="D31" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="28"/>
+      <c r="F31" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="28"/>
+      <c r="H31" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="I31" s="28"/>
+      <c r="J31" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="20"/>
+    </row>
+    <row r="32" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C32" s="19"/>
+      <c r="D32" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="28"/>
+      <c r="F32" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="K32" s="20"/>
+    </row>
+    <row r="33" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="19"/>
+      <c r="D33" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="28"/>
+      <c r="F33" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="28"/>
+      <c r="H33" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" s="28"/>
+      <c r="J33" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K33" s="20"/>
+    </row>
+    <row r="34" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="19"/>
+      <c r="D34" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="28"/>
+      <c r="F34" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K34" s="20"/>
+    </row>
+    <row r="35" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="19"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K35" s="20"/>
+    </row>
+    <row r="36" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C36" s="19"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="20"/>
+    </row>
+    <row r="37" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="19"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="20"/>
+    </row>
+    <row r="38" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="21"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="24"/>
+    </row>
+    <row r="39" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="18"/>
+      <c r="AH40" s="18"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C41" s="19"/>
+      <c r="D41" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="O41" s="20"/>
+      <c r="AH41" s="20"/>
+    </row>
+    <row r="42" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="19"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="20"/>
+      <c r="AH42" s="20"/>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C43" s="19"/>
+      <c r="D43" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="27"/>
+      <c r="F43" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43" s="27"/>
+      <c r="H43" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I43" s="27"/>
+      <c r="J43" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K43" s="27"/>
+      <c r="L43" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="M43" s="27"/>
+      <c r="N43" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="O43" s="20"/>
+      <c r="AH43" s="20"/>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C44" s="19"/>
+      <c r="D44" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="27"/>
+      <c r="F44" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G44" s="27"/>
+      <c r="H44" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="27"/>
+      <c r="J44" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K44" s="27"/>
+      <c r="L44" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="M44" s="27"/>
+      <c r="N44" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="O44" s="20"/>
+      <c r="AH44" s="20"/>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C45" s="19"/>
+      <c r="D45" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="27"/>
+      <c r="F45" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="27"/>
+      <c r="H45" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="27"/>
+      <c r="J45" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K45" s="27"/>
+      <c r="L45" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" s="27"/>
+      <c r="N45" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="O45" s="20"/>
+      <c r="AH45" s="20"/>
+    </row>
+    <row r="46" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="19"/>
+      <c r="D46" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="27"/>
+      <c r="F46" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="27"/>
+      <c r="H46" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I46" s="27"/>
+      <c r="J46" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="K46" s="27"/>
+      <c r="L46" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="M46" s="27"/>
+      <c r="N46" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="O46" s="20"/>
+      <c r="AH46" s="20"/>
+    </row>
+    <row r="47" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="19"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" s="27"/>
+      <c r="H47" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="I47" s="27"/>
+      <c r="J47" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K47" s="27"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="20"/>
+      <c r="AH47" s="20"/>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C48" s="19"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="I48" s="27"/>
+      <c r="J48" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="K48" s="27"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="20"/>
+      <c r="AH48" s="20"/>
+    </row>
+    <row r="49" spans="3:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="19"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="I49" s="27"/>
+      <c r="J49" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="20"/>
+      <c r="AH49" s="20"/>
+    </row>
+    <row r="50" spans="3:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="21"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="24"/>
+      <c r="AH50" s="20"/>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH51" s="20"/>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH52" s="20"/>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH53" s="20"/>
+    </row>
+    <row r="54" spans="3:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AH54" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0DF540-D4B4-A642-A88C-A4015198B0F3}">
+  <dimension ref="A1:AV106"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" customWidth="1"/>
+    <col min="19" max="19" width="10.83203125" customWidth="1"/>
+    <col min="21" max="21" width="10.83203125" customWidth="1"/>
+    <col min="23" max="23" width="10.83203125" customWidth="1"/>
+    <col min="25" max="25" width="10.83203125" customWidth="1"/>
+    <col min="27" max="27" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AH1" s="1"/>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="B2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C3" s="19"/>
+      <c r="D3" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="28"/>
+      <c r="F3" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" s="20"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+    </row>
+    <row r="4" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="19"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="10"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+    </row>
+    <row r="5" spans="1:35" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="27"/>
+      <c r="H5" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="27"/>
+      <c r="P5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="V5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AD5" s="29"/>
+    </row>
+    <row r="6" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="19"/>
+      <c r="D6" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="28"/>
+      <c r="F6" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="27"/>
+      <c r="H6" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="20"/>
+      <c r="J6" s="30"/>
+      <c r="P6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AD6" s="28"/>
+    </row>
+    <row r="7" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="19"/>
+      <c r="D7" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="20"/>
+      <c r="P7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AD7" s="28"/>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C8" s="19"/>
+      <c r="D8" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="20"/>
+      <c r="P8" s="27"/>
+      <c r="R8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="V8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AD8" s="28"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C9" s="19"/>
+      <c r="D9" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="20"/>
+      <c r="K9" s="32"/>
+      <c r="N9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="R9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AD9" s="28"/>
+    </row>
+    <row r="10" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="19"/>
+      <c r="D10" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="20"/>
+      <c r="N10" s="27"/>
+      <c r="P10" s="27"/>
+      <c r="R10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="27"/>
+      <c r="AC10" s="27"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="28"/>
+    </row>
+    <row r="11" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="21"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="N11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+      <c r="V11" s="27"/>
+      <c r="X11" s="27"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27"/>
+      <c r="AB11" s="27"/>
+      <c r="AC11" s="27"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+    </row>
+    <row r="12" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+      <c r="V12" s="27"/>
+      <c r="X12" s="27"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="27"/>
+      <c r="AC12" s="27"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="B13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="C14" s="19"/>
+      <c r="D14" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="29"/>
+      <c r="H14" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="20"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27"/>
+      <c r="AB14" s="27"/>
+      <c r="AC14" s="27"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="28"/>
+    </row>
+    <row r="15" spans="1:35" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="19"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="20"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="27"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+    </row>
+    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="28"/>
+      <c r="H16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="20"/>
+      <c r="J16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="27"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27"/>
+      <c r="AB16" s="27"/>
+      <c r="AC16" s="27"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28"/>
+      <c r="AH16"/>
+      <c r="AI16"/>
+    </row>
+    <row r="17" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="19"/>
+      <c r="D17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="27"/>
+      <c r="F17" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" s="28"/>
+      <c r="H17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="20"/>
+      <c r="J17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="27"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="27"/>
+      <c r="AC17" s="27"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28"/>
+    </row>
+    <row r="18" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C18" s="19"/>
+      <c r="D18" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="27"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I18" s="20"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="27"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="27"/>
+      <c r="AB18" s="27"/>
+      <c r="AC18" s="27"/>
+      <c r="AD18" s="28"/>
+      <c r="AE18" s="28"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28"/>
+    </row>
+    <row r="19" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C19" s="19"/>
+      <c r="D19" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="20"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
+      <c r="AA19" s="10"/>
+      <c r="AB19" s="10"/>
+      <c r="AC19" s="10"/>
+    </row>
+    <row r="20" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C20" s="19"/>
+      <c r="D20" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="20"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
+      <c r="AB20" s="10"/>
+      <c r="AC20" s="10"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1"/>
+      <c r="AN20" s="1"/>
+      <c r="AO20" s="1"/>
+      <c r="AP20" s="1"/>
+      <c r="AQ20" s="1"/>
+      <c r="AR20" s="1"/>
+      <c r="AS20" s="1"/>
+      <c r="AT20" s="1"/>
+      <c r="AU20" s="1"/>
+      <c r="AV20" s="1"/>
+    </row>
+    <row r="21" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C21" s="19"/>
+      <c r="D21" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="20"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+    </row>
+    <row r="22" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="19"/>
+      <c r="D22" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="20"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+      <c r="AB22" s="10"/>
+      <c r="AC22" s="10"/>
+    </row>
+    <row r="23" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C23" s="19"/>
+      <c r="D23" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="20"/>
+    </row>
+    <row r="24" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="19"/>
+      <c r="D24" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="20"/>
+    </row>
+    <row r="25" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="21"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="24"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+    </row>
+    <row r="26" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="18"/>
+    </row>
+    <row r="28" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C28" s="19"/>
+      <c r="D28" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="28"/>
+      <c r="H28" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" s="28"/>
+      <c r="J28" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="K28" s="36"/>
+    </row>
+    <row r="29" spans="2:48" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="19"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="20"/>
+    </row>
+    <row r="30" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C30" s="19"/>
+      <c r="D30" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="28"/>
+      <c r="F30" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="28"/>
+      <c r="H30" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="I30" s="28"/>
+      <c r="J30" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="K30" s="20"/>
+    </row>
+    <row r="31" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C31" s="19"/>
+      <c r="D31" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="28"/>
+      <c r="F31" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="28"/>
+      <c r="H31" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="I31" s="28"/>
+      <c r="J31" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="K31" s="20"/>
+    </row>
+    <row r="32" spans="2:48" x14ac:dyDescent="0.2">
+      <c r="C32" s="19"/>
+      <c r="D32" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="28"/>
+      <c r="F32" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="28"/>
+      <c r="H32" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="K32" s="20"/>
+    </row>
+    <row r="33" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="19"/>
+      <c r="D33" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="28"/>
+      <c r="F33" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="28"/>
+      <c r="H33" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" s="28"/>
+      <c r="J33" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K33" s="20"/>
+    </row>
+    <row r="34" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="19"/>
+      <c r="D34" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="28"/>
+      <c r="F34" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K34" s="20"/>
+    </row>
+    <row r="35" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="19"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="K35" s="20"/>
+    </row>
+    <row r="36" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C36" s="19"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="20"/>
+    </row>
+    <row r="37" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="19"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="20"/>
+    </row>
+    <row r="38" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="21"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="24"/>
+    </row>
+    <row r="39" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="17"/>
+      <c r="M40" s="17"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="18"/>
+      <c r="AH40" s="18"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C41" s="19"/>
+      <c r="D41" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="O41" s="20"/>
+      <c r="AH41" s="20"/>
+    </row>
+    <row r="42" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="19"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="20"/>
+      <c r="AH42" s="20"/>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C43" s="19"/>
+      <c r="D43" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="27"/>
+      <c r="F43" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43" s="27"/>
+      <c r="H43" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="I43" s="27"/>
+      <c r="J43" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="K43" s="27"/>
+      <c r="L43" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="M43" s="27"/>
+      <c r="N43" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="O43" s="20"/>
+      <c r="AH43" s="20"/>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C44" s="19"/>
+      <c r="D44" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="27"/>
+      <c r="F44" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G44" s="27"/>
+      <c r="H44" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="27"/>
+      <c r="J44" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="K44" s="27"/>
+      <c r="L44" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="M44" s="27"/>
+      <c r="N44" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="O44" s="20"/>
+      <c r="AH44" s="20"/>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C45" s="19"/>
+      <c r="D45" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="27"/>
+      <c r="F45" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="27"/>
+      <c r="H45" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="I45" s="27"/>
+      <c r="J45" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K45" s="27"/>
+      <c r="L45" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="M45" s="27"/>
+      <c r="N45" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="O45" s="20"/>
+      <c r="AH45" s="20"/>
+    </row>
+    <row r="46" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="19"/>
+      <c r="D46" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E46" s="27"/>
+      <c r="F46" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="27"/>
+      <c r="H46" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I46" s="27"/>
+      <c r="J46" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="K46" s="27"/>
+      <c r="L46" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="M46" s="27"/>
+      <c r="N46" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="O46" s="20"/>
+      <c r="AH46" s="20"/>
+    </row>
+    <row r="47" spans="2:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="19"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G47" s="27"/>
+      <c r="H47" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="I47" s="27"/>
+      <c r="J47" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K47" s="27"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="20"/>
+      <c r="AH47" s="20"/>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="C48" s="19"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="I48" s="27"/>
+      <c r="J48" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="K48" s="27"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="20"/>
+      <c r="AH48" s="20"/>
+    </row>
+    <row r="49" spans="3:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C49" s="19"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="I49" s="27"/>
+      <c r="J49" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="K49" s="27"/>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="20"/>
+      <c r="AH49" s="20"/>
+    </row>
+    <row r="50" spans="3:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C50" s="21"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="24"/>
+      <c r="AH50" s="20"/>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH51" s="20"/>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH52" s="20"/>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH53" s="20"/>
+    </row>
+    <row r="54" spans="3:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AH54" s="24"/>
+    </row>
+    <row r="75" spans="8:12" x14ac:dyDescent="0.2">
+      <c r="H75" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="J75" t="s">
+        <v>158</v>
+      </c>
+      <c r="L75" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="76" spans="8:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H76" s="43"/>
+      <c r="I76" s="10"/>
+    </row>
+    <row r="77" spans="8:12" x14ac:dyDescent="0.2">
+      <c r="H77" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="I77" s="27"/>
+      <c r="J77" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="L77" s="44" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="78" spans="8:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H78" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I78" s="31"/>
+      <c r="J78" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="8:12" x14ac:dyDescent="0.2">
+      <c r="I79" s="27"/>
+      <c r="J79" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="80" spans="8:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I80" s="27"/>
+      <c r="J80" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="I81" s="27"/>
+      <c r="J81" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J82" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D86" t="s">
+        <v>174</v>
+      </c>
+      <c r="F86" t="s">
+        <v>176</v>
+      </c>
+      <c r="H86" t="s">
+        <v>178</v>
+      </c>
+      <c r="J86" t="s">
+        <v>184</v>
+      </c>
+      <c r="L86" t="s">
+        <v>188</v>
+      </c>
+      <c r="N86" t="s">
+        <v>181</v>
+      </c>
+      <c r="P86" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="87" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D88" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="89" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D89" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H89" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="J89" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="L89" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="N89" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="P89" s="48" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D90" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H90" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="J90" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="L90" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="N90" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="P90" s="48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D91" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="F91" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="H91" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="J91" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="L91" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="N91" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="P91" s="48" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="92" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F92" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H92" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="J92" s="38" t="s">
+        <v>193</v>
+      </c>
+      <c r="L92" s="41"/>
+      <c r="P92" s="49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="93" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F93" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="J93" s="39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="94" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F94" s="39" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F98" t="s">
+        <v>163</v>
+      </c>
+      <c r="H98" t="s">
+        <v>180</v>
+      </c>
+      <c r="J98" t="s">
+        <v>187</v>
+      </c>
+      <c r="L98" s="42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="99" spans="6:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L99" s="42"/>
+    </row>
+    <row r="100" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F100" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="H100" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="J100" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="L100" s="45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="101" spans="6:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F101" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="L101" s="13" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="102" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F102" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="L102" s="13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="103" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F103" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L103" s="46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="104" spans="6:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F104" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="L104" s="47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="105" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F105" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="106" spans="6:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F106" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>